--- a/030-試験/033-総合試験計画書兼結果書.xlsx
+++ b/030-試験/033-総合試験計画書兼結果書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\030-試験\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E0DE4E-54E7-4D0E-8F2E-4843455CACB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC18210-4440-43CE-A30F-D7ACB45915FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E19F39F9-7AA3-46C6-B109-8C2C31CD3061}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19F39F9-7AA3-46C6-B109-8C2C31CD3061}"/>
   </bookViews>
   <sheets>
     <sheet name="総合試験" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="127">
   <si>
     <t>総合試験</t>
     <rPh sb="0" eb="4">
@@ -1036,6 +1036,10 @@
     <rPh sb="0" eb="2">
       <t>ニュウリョク</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1596,7 +1600,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1763,6 +1767,51 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1781,15 +1830,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1807,15 +1847,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1859,30 +1890,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1895,7 +1902,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2220,7 +2254,9 @@
   <cols>
     <col min="1" max="7" width="2.69921875" style="24"/>
     <col min="8" max="8" width="3" style="24" customWidth="1"/>
-    <col min="9" max="30" width="2.69921875" style="24"/>
+    <col min="9" max="12" width="2.69921875" style="24"/>
+    <col min="13" max="13" width="2.69921875" style="24" customWidth="1"/>
+    <col min="14" max="30" width="2.69921875" style="24"/>
     <col min="31" max="41" width="2.69921875" style="1"/>
     <col min="42" max="51" width="2.69921875" style="24"/>
     <col min="52" max="52" width="3.09765625" style="24" customWidth="1"/>
@@ -2236,76 +2272,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:183" ht="15.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="89" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="89"/>
-      <c r="V1" s="89"/>
-      <c r="W1" s="89"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="74"/>
-      <c r="AH1" s="74"/>
-      <c r="AI1" s="74"/>
-      <c r="AJ1" s="74"/>
-      <c r="AK1" s="74"/>
-      <c r="AL1" s="74"/>
-      <c r="AM1" s="75"/>
-      <c r="AN1" s="89" t="s">
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="86"/>
+      <c r="Z1" s="86"/>
+      <c r="AA1" s="86"/>
+      <c r="AB1" s="86"/>
+      <c r="AC1" s="86"/>
+      <c r="AD1" s="86"/>
+      <c r="AE1" s="86"/>
+      <c r="AF1" s="86"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="86"/>
+      <c r="AI1" s="86"/>
+      <c r="AJ1" s="86"/>
+      <c r="AK1" s="86"/>
+      <c r="AL1" s="86"/>
+      <c r="AM1" s="87"/>
+      <c r="AN1" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="AO1" s="89"/>
-      <c r="AP1" s="89"/>
-      <c r="AQ1" s="89"/>
-      <c r="AR1" s="90">
+      <c r="AO1" s="98"/>
+      <c r="AP1" s="98"/>
+      <c r="AQ1" s="98"/>
+      <c r="AR1" s="99">
         <v>45575</v>
       </c>
-      <c r="AS1" s="90"/>
-      <c r="AT1" s="90"/>
-      <c r="AU1" s="90"/>
-      <c r="AV1" s="90"/>
-      <c r="AW1" s="90"/>
-      <c r="AX1" s="90"/>
-      <c r="AY1" s="90"/>
-      <c r="AZ1" s="90"/>
-      <c r="BA1" s="90"/>
-      <c r="BB1" s="91" t="s">
+      <c r="AS1" s="99"/>
+      <c r="AT1" s="99"/>
+      <c r="AU1" s="99"/>
+      <c r="AV1" s="99"/>
+      <c r="AW1" s="99"/>
+      <c r="AX1" s="99"/>
+      <c r="AY1" s="99"/>
+      <c r="AZ1" s="99"/>
+      <c r="BA1" s="99"/>
+      <c r="BB1" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="BC1" s="91"/>
-      <c r="BD1" s="92"/>
-      <c r="BE1" s="64"/>
-      <c r="BF1" s="65"/>
-      <c r="BG1" s="65"/>
-      <c r="BH1" s="66"/>
+      <c r="BC1" s="100"/>
+      <c r="BD1" s="101"/>
+      <c r="BE1" s="79"/>
+      <c r="BF1" s="80"/>
+      <c r="BG1" s="80"/>
+      <c r="BH1" s="81"/>
       <c r="BW1" s="24"/>
       <c r="BX1" s="24"/>
       <c r="BY1" s="24"/>
@@ -2341,74 +2377,74 @@
       <c r="FQ1" s="24"/>
     </row>
     <row r="2" spans="1:183" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="87"/>
-      <c r="T2" s="88" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="88"/>
-      <c r="X2" s="76" t="s">
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+      <c r="X2" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="77"/>
-      <c r="AB2" s="77"/>
-      <c r="AC2" s="77"/>
-      <c r="AD2" s="77"/>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="77"/>
-      <c r="AH2" s="77"/>
-      <c r="AI2" s="77"/>
-      <c r="AJ2" s="77"/>
-      <c r="AK2" s="77"/>
-      <c r="AL2" s="77"/>
-      <c r="AM2" s="78"/>
-      <c r="AN2" s="88" t="s">
+      <c r="Y2" s="89"/>
+      <c r="Z2" s="89"/>
+      <c r="AA2" s="89"/>
+      <c r="AB2" s="89"/>
+      <c r="AC2" s="89"/>
+      <c r="AD2" s="89"/>
+      <c r="AE2" s="89"/>
+      <c r="AF2" s="89"/>
+      <c r="AG2" s="89"/>
+      <c r="AH2" s="89"/>
+      <c r="AI2" s="89"/>
+      <c r="AJ2" s="89"/>
+      <c r="AK2" s="89"/>
+      <c r="AL2" s="89"/>
+      <c r="AM2" s="90"/>
+      <c r="AN2" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="AO2" s="88"/>
-      <c r="AP2" s="88"/>
-      <c r="AQ2" s="88"/>
-      <c r="AR2" s="95" t="s">
+      <c r="AO2" s="97"/>
+      <c r="AP2" s="97"/>
+      <c r="AQ2" s="97"/>
+      <c r="AR2" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="95"/>
-      <c r="AU2" s="95"/>
-      <c r="AV2" s="95"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="95"/>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
-      <c r="BB2" s="93"/>
-      <c r="BC2" s="93"/>
-      <c r="BD2" s="94"/>
-      <c r="BE2" s="67"/>
-      <c r="BF2" s="68"/>
-      <c r="BG2" s="68"/>
-      <c r="BH2" s="69"/>
+      <c r="AS2" s="104"/>
+      <c r="AT2" s="104"/>
+      <c r="AU2" s="104"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="104"/>
+      <c r="AX2" s="104"/>
+      <c r="AY2" s="104"/>
+      <c r="AZ2" s="104"/>
+      <c r="BA2" s="104"/>
+      <c r="BB2" s="102"/>
+      <c r="BC2" s="102"/>
+      <c r="BD2" s="103"/>
+      <c r="BE2" s="82"/>
+      <c r="BF2" s="83"/>
+      <c r="BG2" s="83"/>
+      <c r="BH2" s="84"/>
       <c r="BW2" s="24"/>
       <c r="BX2" s="24"/>
       <c r="BY2" s="24"/>
@@ -2444,58 +2480,58 @@
       <c r="FQ2" s="24"/>
     </row>
     <row r="3" spans="1:183" ht="15.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="106" t="s">
+      <c r="B3" s="105"/>
+      <c r="C3" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="106"/>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="106"/>
-      <c r="W3" s="106"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="107"/>
+      <c r="Q3" s="107"/>
+      <c r="R3" s="107"/>
+      <c r="S3" s="107"/>
+      <c r="T3" s="107"/>
+      <c r="U3" s="107"/>
+      <c r="V3" s="107"/>
+      <c r="W3" s="107"/>
     </row>
     <row r="4" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="105"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="107"/>
-      <c r="U4" s="107"/>
-      <c r="V4" s="107"/>
-      <c r="W4" s="107"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="108"/>
+      <c r="T4" s="108"/>
+      <c r="U4" s="108"/>
+      <c r="V4" s="108"/>
+      <c r="W4" s="108"/>
     </row>
     <row r="5" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="25"/>
@@ -2568,978 +2604,978 @@
     </row>
     <row r="6" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="27"/>
-      <c r="H6" s="96" t="s">
+      <c r="H6" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="97"/>
-      <c r="O6" s="97"/>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="97"/>
-      <c r="R6" s="97"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="97"/>
-      <c r="U6" s="97"/>
-      <c r="V6" s="97"/>
-      <c r="W6" s="97"/>
-      <c r="X6" s="97"/>
-      <c r="Y6" s="97"/>
-      <c r="Z6" s="97"/>
-      <c r="AA6" s="97"/>
-      <c r="AB6" s="97"/>
-      <c r="AC6" s="97"/>
-      <c r="AD6" s="97"/>
-      <c r="AE6" s="97"/>
-      <c r="AF6" s="97"/>
-      <c r="AG6" s="97"/>
-      <c r="AH6" s="97"/>
-      <c r="AI6" s="97"/>
-      <c r="AJ6" s="97"/>
-      <c r="AK6" s="97"/>
-      <c r="AL6" s="97"/>
-      <c r="AM6" s="97"/>
-      <c r="AN6" s="97"/>
-      <c r="AO6" s="97"/>
-      <c r="AP6" s="97"/>
-      <c r="AQ6" s="97"/>
-      <c r="AR6" s="97"/>
-      <c r="AS6" s="97"/>
-      <c r="AT6" s="97"/>
-      <c r="AU6" s="97"/>
-      <c r="AV6" s="97"/>
-      <c r="AW6" s="97"/>
-      <c r="AX6" s="97"/>
-      <c r="AY6" s="97"/>
-      <c r="AZ6" s="97"/>
-      <c r="BA6" s="97"/>
-      <c r="BB6" s="97"/>
-      <c r="BC6" s="97"/>
-      <c r="BD6" s="97"/>
-      <c r="BE6" s="97"/>
-      <c r="BF6" s="97"/>
-      <c r="BG6" s="97"/>
-      <c r="BH6" s="97"/>
-      <c r="BI6" s="97"/>
-      <c r="BJ6" s="97"/>
-      <c r="BK6" s="97"/>
-      <c r="BL6" s="97"/>
-      <c r="BM6" s="97"/>
-      <c r="BN6" s="97"/>
-      <c r="BO6" s="97"/>
-      <c r="BP6" s="97"/>
-      <c r="BQ6" s="97"/>
-      <c r="BR6" s="97"/>
-      <c r="BS6" s="97"/>
-      <c r="BT6" s="97"/>
-      <c r="BU6" s="97"/>
-      <c r="BV6" s="97"/>
-      <c r="BW6" s="97"/>
-      <c r="BX6" s="97"/>
-      <c r="BY6" s="97"/>
-      <c r="BZ6" s="97"/>
-      <c r="CA6" s="97"/>
-      <c r="CB6" s="97"/>
-      <c r="CC6" s="97"/>
-      <c r="CD6" s="97"/>
-      <c r="CE6" s="97"/>
-      <c r="CF6" s="97"/>
-      <c r="CG6" s="97"/>
-      <c r="CH6" s="97"/>
-      <c r="CI6" s="97"/>
-      <c r="CJ6" s="97"/>
-      <c r="CK6" s="97"/>
-      <c r="CL6" s="97"/>
-      <c r="CM6" s="97"/>
-      <c r="CN6" s="97"/>
-      <c r="CO6" s="97"/>
-      <c r="CP6" s="97"/>
-      <c r="CQ6" s="97"/>
-      <c r="CR6" s="97"/>
-      <c r="CS6" s="97"/>
-      <c r="CT6" s="97"/>
-      <c r="CU6" s="97"/>
-      <c r="CV6" s="97"/>
-      <c r="CW6" s="97"/>
-      <c r="CX6" s="97"/>
-      <c r="CY6" s="97"/>
-      <c r="CZ6" s="97"/>
-      <c r="DA6" s="97"/>
-      <c r="DB6" s="97"/>
-      <c r="DC6" s="97"/>
-      <c r="DD6" s="97"/>
-      <c r="DE6" s="97"/>
-      <c r="DF6" s="97"/>
-      <c r="DG6" s="97"/>
-      <c r="DH6" s="97"/>
-      <c r="DI6" s="97"/>
-      <c r="DJ6" s="97"/>
-      <c r="DK6" s="97"/>
-      <c r="DL6" s="97"/>
-      <c r="DM6" s="97"/>
-      <c r="DN6" s="97"/>
-      <c r="DO6" s="97"/>
-      <c r="DP6" s="97"/>
-      <c r="DQ6" s="97"/>
-      <c r="DR6" s="97"/>
-      <c r="DS6" s="97"/>
-      <c r="DT6" s="97"/>
-      <c r="DU6" s="97"/>
-      <c r="DV6" s="97"/>
-      <c r="DW6" s="97"/>
-      <c r="DX6" s="97"/>
-      <c r="DY6" s="97"/>
-      <c r="DZ6" s="97"/>
-      <c r="EA6" s="97"/>
-      <c r="EB6" s="97"/>
-      <c r="EC6" s="97"/>
-      <c r="ED6" s="97"/>
-      <c r="EE6" s="97"/>
-      <c r="EF6" s="97"/>
-      <c r="EG6" s="97"/>
-      <c r="EH6" s="97"/>
-      <c r="EI6" s="97"/>
-      <c r="EJ6" s="97"/>
-      <c r="EK6" s="97"/>
-      <c r="EL6" s="97"/>
-      <c r="EM6" s="97"/>
-      <c r="EN6" s="97"/>
-      <c r="EO6" s="97"/>
-      <c r="EP6" s="97"/>
-      <c r="EQ6" s="97"/>
-      <c r="ER6" s="97"/>
-      <c r="ES6" s="97"/>
-      <c r="ET6" s="97"/>
-      <c r="EU6" s="97"/>
-      <c r="EV6" s="97"/>
-      <c r="EW6" s="97"/>
-      <c r="EX6" s="97"/>
-      <c r="EY6" s="97"/>
-      <c r="EZ6" s="97"/>
-      <c r="FA6" s="97"/>
-      <c r="FB6" s="97"/>
-      <c r="FC6" s="97"/>
-      <c r="FD6" s="97"/>
-      <c r="FE6" s="97"/>
-      <c r="FF6" s="97"/>
-      <c r="FG6" s="97"/>
-      <c r="FH6" s="97"/>
-      <c r="FI6" s="97"/>
-      <c r="FJ6" s="97"/>
-      <c r="FK6" s="97"/>
-      <c r="FL6" s="97"/>
-      <c r="FM6" s="97"/>
-      <c r="FN6" s="97"/>
-      <c r="FO6" s="97"/>
-      <c r="FP6" s="97"/>
-      <c r="FQ6" s="97"/>
-      <c r="FR6" s="97"/>
-      <c r="FS6" s="97"/>
-      <c r="FT6" s="97"/>
-      <c r="FU6" s="97"/>
-      <c r="FV6" s="97"/>
-      <c r="FW6" s="97"/>
-      <c r="FX6" s="97"/>
-      <c r="FY6" s="97"/>
-      <c r="FZ6" s="97"/>
-      <c r="GA6" s="98"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="74"/>
+      <c r="T6" s="74"/>
+      <c r="U6" s="74"/>
+      <c r="V6" s="74"/>
+      <c r="W6" s="74"/>
+      <c r="X6" s="74"/>
+      <c r="Y6" s="74"/>
+      <c r="Z6" s="74"/>
+      <c r="AA6" s="74"/>
+      <c r="AB6" s="74"/>
+      <c r="AC6" s="74"/>
+      <c r="AD6" s="74"/>
+      <c r="AE6" s="74"/>
+      <c r="AF6" s="74"/>
+      <c r="AG6" s="74"/>
+      <c r="AH6" s="74"/>
+      <c r="AI6" s="74"/>
+      <c r="AJ6" s="74"/>
+      <c r="AK6" s="74"/>
+      <c r="AL6" s="74"/>
+      <c r="AM6" s="74"/>
+      <c r="AN6" s="74"/>
+      <c r="AO6" s="74"/>
+      <c r="AP6" s="74"/>
+      <c r="AQ6" s="74"/>
+      <c r="AR6" s="74"/>
+      <c r="AS6" s="74"/>
+      <c r="AT6" s="74"/>
+      <c r="AU6" s="74"/>
+      <c r="AV6" s="74"/>
+      <c r="AW6" s="74"/>
+      <c r="AX6" s="74"/>
+      <c r="AY6" s="74"/>
+      <c r="AZ6" s="74"/>
+      <c r="BA6" s="74"/>
+      <c r="BB6" s="74"/>
+      <c r="BC6" s="74"/>
+      <c r="BD6" s="74"/>
+      <c r="BE6" s="74"/>
+      <c r="BF6" s="74"/>
+      <c r="BG6" s="74"/>
+      <c r="BH6" s="74"/>
+      <c r="BI6" s="74"/>
+      <c r="BJ6" s="74"/>
+      <c r="BK6" s="74"/>
+      <c r="BL6" s="74"/>
+      <c r="BM6" s="74"/>
+      <c r="BN6" s="74"/>
+      <c r="BO6" s="74"/>
+      <c r="BP6" s="74"/>
+      <c r="BQ6" s="74"/>
+      <c r="BR6" s="74"/>
+      <c r="BS6" s="74"/>
+      <c r="BT6" s="74"/>
+      <c r="BU6" s="74"/>
+      <c r="BV6" s="74"/>
+      <c r="BW6" s="74"/>
+      <c r="BX6" s="74"/>
+      <c r="BY6" s="74"/>
+      <c r="BZ6" s="74"/>
+      <c r="CA6" s="74"/>
+      <c r="CB6" s="74"/>
+      <c r="CC6" s="74"/>
+      <c r="CD6" s="74"/>
+      <c r="CE6" s="74"/>
+      <c r="CF6" s="74"/>
+      <c r="CG6" s="74"/>
+      <c r="CH6" s="74"/>
+      <c r="CI6" s="74"/>
+      <c r="CJ6" s="74"/>
+      <c r="CK6" s="74"/>
+      <c r="CL6" s="74"/>
+      <c r="CM6" s="74"/>
+      <c r="CN6" s="74"/>
+      <c r="CO6" s="74"/>
+      <c r="CP6" s="74"/>
+      <c r="CQ6" s="74"/>
+      <c r="CR6" s="74"/>
+      <c r="CS6" s="74"/>
+      <c r="CT6" s="74"/>
+      <c r="CU6" s="74"/>
+      <c r="CV6" s="74"/>
+      <c r="CW6" s="74"/>
+      <c r="CX6" s="74"/>
+      <c r="CY6" s="74"/>
+      <c r="CZ6" s="74"/>
+      <c r="DA6" s="74"/>
+      <c r="DB6" s="74"/>
+      <c r="DC6" s="74"/>
+      <c r="DD6" s="74"/>
+      <c r="DE6" s="74"/>
+      <c r="DF6" s="74"/>
+      <c r="DG6" s="74"/>
+      <c r="DH6" s="74"/>
+      <c r="DI6" s="74"/>
+      <c r="DJ6" s="74"/>
+      <c r="DK6" s="74"/>
+      <c r="DL6" s="74"/>
+      <c r="DM6" s="74"/>
+      <c r="DN6" s="74"/>
+      <c r="DO6" s="74"/>
+      <c r="DP6" s="74"/>
+      <c r="DQ6" s="74"/>
+      <c r="DR6" s="74"/>
+      <c r="DS6" s="74"/>
+      <c r="DT6" s="74"/>
+      <c r="DU6" s="74"/>
+      <c r="DV6" s="74"/>
+      <c r="DW6" s="74"/>
+      <c r="DX6" s="74"/>
+      <c r="DY6" s="74"/>
+      <c r="DZ6" s="74"/>
+      <c r="EA6" s="74"/>
+      <c r="EB6" s="74"/>
+      <c r="EC6" s="74"/>
+      <c r="ED6" s="74"/>
+      <c r="EE6" s="74"/>
+      <c r="EF6" s="74"/>
+      <c r="EG6" s="74"/>
+      <c r="EH6" s="74"/>
+      <c r="EI6" s="74"/>
+      <c r="EJ6" s="74"/>
+      <c r="EK6" s="74"/>
+      <c r="EL6" s="74"/>
+      <c r="EM6" s="74"/>
+      <c r="EN6" s="74"/>
+      <c r="EO6" s="74"/>
+      <c r="EP6" s="74"/>
+      <c r="EQ6" s="74"/>
+      <c r="ER6" s="74"/>
+      <c r="ES6" s="74"/>
+      <c r="ET6" s="74"/>
+      <c r="EU6" s="74"/>
+      <c r="EV6" s="74"/>
+      <c r="EW6" s="74"/>
+      <c r="EX6" s="74"/>
+      <c r="EY6" s="74"/>
+      <c r="EZ6" s="74"/>
+      <c r="FA6" s="74"/>
+      <c r="FB6" s="74"/>
+      <c r="FC6" s="74"/>
+      <c r="FD6" s="74"/>
+      <c r="FE6" s="74"/>
+      <c r="FF6" s="74"/>
+      <c r="FG6" s="74"/>
+      <c r="FH6" s="74"/>
+      <c r="FI6" s="74"/>
+      <c r="FJ6" s="74"/>
+      <c r="FK6" s="74"/>
+      <c r="FL6" s="74"/>
+      <c r="FM6" s="74"/>
+      <c r="FN6" s="74"/>
+      <c r="FO6" s="74"/>
+      <c r="FP6" s="74"/>
+      <c r="FQ6" s="74"/>
+      <c r="FR6" s="74"/>
+      <c r="FS6" s="74"/>
+      <c r="FT6" s="74"/>
+      <c r="FU6" s="74"/>
+      <c r="FV6" s="74"/>
+      <c r="FW6" s="74"/>
+      <c r="FX6" s="74"/>
+      <c r="FY6" s="74"/>
+      <c r="FZ6" s="74"/>
+      <c r="GA6" s="75"/>
     </row>
     <row r="7" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G7" s="27"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="100"/>
-      <c r="N7" s="100"/>
-      <c r="O7" s="100"/>
-      <c r="P7" s="100"/>
-      <c r="Q7" s="100"/>
-      <c r="R7" s="100"/>
-      <c r="S7" s="100"/>
-      <c r="T7" s="100"/>
-      <c r="U7" s="100"/>
-      <c r="V7" s="100"/>
-      <c r="W7" s="100"/>
-      <c r="X7" s="100"/>
-      <c r="Y7" s="100"/>
-      <c r="Z7" s="100"/>
-      <c r="AA7" s="100"/>
-      <c r="AB7" s="100"/>
-      <c r="AC7" s="100"/>
-      <c r="AD7" s="100"/>
-      <c r="AE7" s="100"/>
-      <c r="AF7" s="100"/>
-      <c r="AG7" s="100"/>
-      <c r="AH7" s="100"/>
-      <c r="AI7" s="100"/>
-      <c r="AJ7" s="100"/>
-      <c r="AK7" s="100"/>
-      <c r="AL7" s="100"/>
-      <c r="AM7" s="100"/>
-      <c r="AN7" s="100"/>
-      <c r="AO7" s="100"/>
-      <c r="AP7" s="100"/>
-      <c r="AQ7" s="100"/>
-      <c r="AR7" s="100"/>
-      <c r="AS7" s="100"/>
-      <c r="AT7" s="100"/>
-      <c r="AU7" s="100"/>
-      <c r="AV7" s="100"/>
-      <c r="AW7" s="100"/>
-      <c r="AX7" s="100"/>
-      <c r="AY7" s="100"/>
-      <c r="AZ7" s="100"/>
-      <c r="BA7" s="100"/>
-      <c r="BB7" s="100"/>
-      <c r="BC7" s="100"/>
-      <c r="BD7" s="100"/>
-      <c r="BE7" s="100"/>
-      <c r="BF7" s="100"/>
-      <c r="BG7" s="100"/>
-      <c r="BH7" s="100"/>
-      <c r="BI7" s="100"/>
-      <c r="BJ7" s="100"/>
-      <c r="BK7" s="100"/>
-      <c r="BL7" s="100"/>
-      <c r="BM7" s="100"/>
-      <c r="BN7" s="100"/>
-      <c r="BO7" s="100"/>
-      <c r="BP7" s="100"/>
-      <c r="BQ7" s="100"/>
-      <c r="BR7" s="100"/>
-      <c r="BS7" s="100"/>
-      <c r="BT7" s="100"/>
-      <c r="BU7" s="100"/>
-      <c r="BV7" s="100"/>
-      <c r="BW7" s="100"/>
-      <c r="BX7" s="100"/>
-      <c r="BY7" s="100"/>
-      <c r="BZ7" s="100"/>
-      <c r="CA7" s="100"/>
-      <c r="CB7" s="100"/>
-      <c r="CC7" s="100"/>
-      <c r="CD7" s="100"/>
-      <c r="CE7" s="100"/>
-      <c r="CF7" s="100"/>
-      <c r="CG7" s="100"/>
-      <c r="CH7" s="100"/>
-      <c r="CI7" s="100"/>
-      <c r="CJ7" s="100"/>
-      <c r="CK7" s="100"/>
-      <c r="CL7" s="100"/>
-      <c r="CM7" s="100"/>
-      <c r="CN7" s="100"/>
-      <c r="CO7" s="100"/>
-      <c r="CP7" s="100"/>
-      <c r="CQ7" s="100"/>
-      <c r="CR7" s="100"/>
-      <c r="CS7" s="100"/>
-      <c r="CT7" s="100"/>
-      <c r="CU7" s="100"/>
-      <c r="CV7" s="100"/>
-      <c r="CW7" s="100"/>
-      <c r="CX7" s="100"/>
-      <c r="CY7" s="100"/>
-      <c r="CZ7" s="100"/>
-      <c r="DA7" s="100"/>
-      <c r="DB7" s="100"/>
-      <c r="DC7" s="100"/>
-      <c r="DD7" s="100"/>
-      <c r="DE7" s="100"/>
-      <c r="DF7" s="100"/>
-      <c r="DG7" s="100"/>
-      <c r="DH7" s="100"/>
-      <c r="DI7" s="100"/>
-      <c r="DJ7" s="100"/>
-      <c r="DK7" s="100"/>
-      <c r="DL7" s="100"/>
-      <c r="DM7" s="100"/>
-      <c r="DN7" s="100"/>
-      <c r="DO7" s="100"/>
-      <c r="DP7" s="100"/>
-      <c r="DQ7" s="100"/>
-      <c r="DR7" s="100"/>
-      <c r="DS7" s="100"/>
-      <c r="DT7" s="100"/>
-      <c r="DU7" s="100"/>
-      <c r="DV7" s="100"/>
-      <c r="DW7" s="100"/>
-      <c r="DX7" s="100"/>
-      <c r="DY7" s="100"/>
-      <c r="DZ7" s="100"/>
-      <c r="EA7" s="100"/>
-      <c r="EB7" s="100"/>
-      <c r="EC7" s="100"/>
-      <c r="ED7" s="100"/>
-      <c r="EE7" s="100"/>
-      <c r="EF7" s="100"/>
-      <c r="EG7" s="100"/>
-      <c r="EH7" s="100"/>
-      <c r="EI7" s="100"/>
-      <c r="EJ7" s="100"/>
-      <c r="EK7" s="100"/>
-      <c r="EL7" s="100"/>
-      <c r="EM7" s="100"/>
-      <c r="EN7" s="100"/>
-      <c r="EO7" s="100"/>
-      <c r="EP7" s="100"/>
-      <c r="EQ7" s="100"/>
-      <c r="ER7" s="100"/>
-      <c r="ES7" s="100"/>
-      <c r="ET7" s="100"/>
-      <c r="EU7" s="100"/>
-      <c r="EV7" s="100"/>
-      <c r="EW7" s="100"/>
-      <c r="EX7" s="100"/>
-      <c r="EY7" s="100"/>
-      <c r="EZ7" s="100"/>
-      <c r="FA7" s="100"/>
-      <c r="FB7" s="100"/>
-      <c r="FC7" s="100"/>
-      <c r="FD7" s="100"/>
-      <c r="FE7" s="100"/>
-      <c r="FF7" s="100"/>
-      <c r="FG7" s="100"/>
-      <c r="FH7" s="100"/>
-      <c r="FI7" s="100"/>
-      <c r="FJ7" s="100"/>
-      <c r="FK7" s="100"/>
-      <c r="FL7" s="100"/>
-      <c r="FM7" s="100"/>
-      <c r="FN7" s="100"/>
-      <c r="FO7" s="100"/>
-      <c r="FP7" s="100"/>
-      <c r="FQ7" s="100"/>
-      <c r="FR7" s="100"/>
-      <c r="FS7" s="100"/>
-      <c r="FT7" s="100"/>
-      <c r="FU7" s="100"/>
-      <c r="FV7" s="100"/>
-      <c r="FW7" s="100"/>
-      <c r="FX7" s="100"/>
-      <c r="FY7" s="100"/>
-      <c r="FZ7" s="100"/>
-      <c r="GA7" s="101"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="77"/>
+      <c r="T7" s="77"/>
+      <c r="U7" s="77"/>
+      <c r="V7" s="77"/>
+      <c r="W7" s="77"/>
+      <c r="X7" s="77"/>
+      <c r="Y7" s="77"/>
+      <c r="Z7" s="77"/>
+      <c r="AA7" s="77"/>
+      <c r="AB7" s="77"/>
+      <c r="AC7" s="77"/>
+      <c r="AD7" s="77"/>
+      <c r="AE7" s="77"/>
+      <c r="AF7" s="77"/>
+      <c r="AG7" s="77"/>
+      <c r="AH7" s="77"/>
+      <c r="AI7" s="77"/>
+      <c r="AJ7" s="77"/>
+      <c r="AK7" s="77"/>
+      <c r="AL7" s="77"/>
+      <c r="AM7" s="77"/>
+      <c r="AN7" s="77"/>
+      <c r="AO7" s="77"/>
+      <c r="AP7" s="77"/>
+      <c r="AQ7" s="77"/>
+      <c r="AR7" s="77"/>
+      <c r="AS7" s="77"/>
+      <c r="AT7" s="77"/>
+      <c r="AU7" s="77"/>
+      <c r="AV7" s="77"/>
+      <c r="AW7" s="77"/>
+      <c r="AX7" s="77"/>
+      <c r="AY7" s="77"/>
+      <c r="AZ7" s="77"/>
+      <c r="BA7" s="77"/>
+      <c r="BB7" s="77"/>
+      <c r="BC7" s="77"/>
+      <c r="BD7" s="77"/>
+      <c r="BE7" s="77"/>
+      <c r="BF7" s="77"/>
+      <c r="BG7" s="77"/>
+      <c r="BH7" s="77"/>
+      <c r="BI7" s="77"/>
+      <c r="BJ7" s="77"/>
+      <c r="BK7" s="77"/>
+      <c r="BL7" s="77"/>
+      <c r="BM7" s="77"/>
+      <c r="BN7" s="77"/>
+      <c r="BO7" s="77"/>
+      <c r="BP7" s="77"/>
+      <c r="BQ7" s="77"/>
+      <c r="BR7" s="77"/>
+      <c r="BS7" s="77"/>
+      <c r="BT7" s="77"/>
+      <c r="BU7" s="77"/>
+      <c r="BV7" s="77"/>
+      <c r="BW7" s="77"/>
+      <c r="BX7" s="77"/>
+      <c r="BY7" s="77"/>
+      <c r="BZ7" s="77"/>
+      <c r="CA7" s="77"/>
+      <c r="CB7" s="77"/>
+      <c r="CC7" s="77"/>
+      <c r="CD7" s="77"/>
+      <c r="CE7" s="77"/>
+      <c r="CF7" s="77"/>
+      <c r="CG7" s="77"/>
+      <c r="CH7" s="77"/>
+      <c r="CI7" s="77"/>
+      <c r="CJ7" s="77"/>
+      <c r="CK7" s="77"/>
+      <c r="CL7" s="77"/>
+      <c r="CM7" s="77"/>
+      <c r="CN7" s="77"/>
+      <c r="CO7" s="77"/>
+      <c r="CP7" s="77"/>
+      <c r="CQ7" s="77"/>
+      <c r="CR7" s="77"/>
+      <c r="CS7" s="77"/>
+      <c r="CT7" s="77"/>
+      <c r="CU7" s="77"/>
+      <c r="CV7" s="77"/>
+      <c r="CW7" s="77"/>
+      <c r="CX7" s="77"/>
+      <c r="CY7" s="77"/>
+      <c r="CZ7" s="77"/>
+      <c r="DA7" s="77"/>
+      <c r="DB7" s="77"/>
+      <c r="DC7" s="77"/>
+      <c r="DD7" s="77"/>
+      <c r="DE7" s="77"/>
+      <c r="DF7" s="77"/>
+      <c r="DG7" s="77"/>
+      <c r="DH7" s="77"/>
+      <c r="DI7" s="77"/>
+      <c r="DJ7" s="77"/>
+      <c r="DK7" s="77"/>
+      <c r="DL7" s="77"/>
+      <c r="DM7" s="77"/>
+      <c r="DN7" s="77"/>
+      <c r="DO7" s="77"/>
+      <c r="DP7" s="77"/>
+      <c r="DQ7" s="77"/>
+      <c r="DR7" s="77"/>
+      <c r="DS7" s="77"/>
+      <c r="DT7" s="77"/>
+      <c r="DU7" s="77"/>
+      <c r="DV7" s="77"/>
+      <c r="DW7" s="77"/>
+      <c r="DX7" s="77"/>
+      <c r="DY7" s="77"/>
+      <c r="DZ7" s="77"/>
+      <c r="EA7" s="77"/>
+      <c r="EB7" s="77"/>
+      <c r="EC7" s="77"/>
+      <c r="ED7" s="77"/>
+      <c r="EE7" s="77"/>
+      <c r="EF7" s="77"/>
+      <c r="EG7" s="77"/>
+      <c r="EH7" s="77"/>
+      <c r="EI7" s="77"/>
+      <c r="EJ7" s="77"/>
+      <c r="EK7" s="77"/>
+      <c r="EL7" s="77"/>
+      <c r="EM7" s="77"/>
+      <c r="EN7" s="77"/>
+      <c r="EO7" s="77"/>
+      <c r="EP7" s="77"/>
+      <c r="EQ7" s="77"/>
+      <c r="ER7" s="77"/>
+      <c r="ES7" s="77"/>
+      <c r="ET7" s="77"/>
+      <c r="EU7" s="77"/>
+      <c r="EV7" s="77"/>
+      <c r="EW7" s="77"/>
+      <c r="EX7" s="77"/>
+      <c r="EY7" s="77"/>
+      <c r="EZ7" s="77"/>
+      <c r="FA7" s="77"/>
+      <c r="FB7" s="77"/>
+      <c r="FC7" s="77"/>
+      <c r="FD7" s="77"/>
+      <c r="FE7" s="77"/>
+      <c r="FF7" s="77"/>
+      <c r="FG7" s="77"/>
+      <c r="FH7" s="77"/>
+      <c r="FI7" s="77"/>
+      <c r="FJ7" s="77"/>
+      <c r="FK7" s="77"/>
+      <c r="FL7" s="77"/>
+      <c r="FM7" s="77"/>
+      <c r="FN7" s="77"/>
+      <c r="FO7" s="77"/>
+      <c r="FP7" s="77"/>
+      <c r="FQ7" s="77"/>
+      <c r="FR7" s="77"/>
+      <c r="FS7" s="77"/>
+      <c r="FT7" s="77"/>
+      <c r="FU7" s="77"/>
+      <c r="FV7" s="77"/>
+      <c r="FW7" s="77"/>
+      <c r="FX7" s="77"/>
+      <c r="FY7" s="77"/>
+      <c r="FZ7" s="77"/>
+      <c r="GA7" s="78"/>
     </row>
     <row r="8" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="H8" s="79" t="s">
+      <c r="H8" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="80"/>
-      <c r="Q8" s="80"/>
-      <c r="R8" s="80"/>
-      <c r="S8" s="80"/>
-      <c r="T8" s="80"/>
-      <c r="U8" s="80"/>
-      <c r="V8" s="80"/>
-      <c r="W8" s="80"/>
-      <c r="X8" s="80"/>
-      <c r="Y8" s="80"/>
-      <c r="Z8" s="80"/>
-      <c r="AA8" s="80"/>
-      <c r="AB8" s="80"/>
-      <c r="AC8" s="80"/>
-      <c r="AD8" s="80"/>
-      <c r="AE8" s="80"/>
-      <c r="AF8" s="80"/>
-      <c r="AG8" s="80"/>
-      <c r="AH8" s="80"/>
-      <c r="AI8" s="80"/>
-      <c r="AJ8" s="80"/>
-      <c r="AK8" s="80"/>
-      <c r="AL8" s="80"/>
-      <c r="AM8" s="80"/>
-      <c r="AN8" s="80"/>
-      <c r="AO8" s="80"/>
-      <c r="AP8" s="80"/>
-      <c r="AQ8" s="80"/>
-      <c r="AR8" s="80"/>
-      <c r="AS8" s="80"/>
-      <c r="AT8" s="80"/>
-      <c r="AU8" s="80"/>
-      <c r="AV8" s="80"/>
-      <c r="AW8" s="80"/>
-      <c r="AX8" s="80"/>
-      <c r="AY8" s="81"/>
-      <c r="AZ8" s="79" t="s">
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="71"/>
+      <c r="AE8" s="71"/>
+      <c r="AF8" s="71"/>
+      <c r="AG8" s="71"/>
+      <c r="AH8" s="71"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="71"/>
+      <c r="AK8" s="71"/>
+      <c r="AL8" s="71"/>
+      <c r="AM8" s="71"/>
+      <c r="AN8" s="71"/>
+      <c r="AO8" s="71"/>
+      <c r="AP8" s="71"/>
+      <c r="AQ8" s="71"/>
+      <c r="AR8" s="71"/>
+      <c r="AS8" s="71"/>
+      <c r="AT8" s="71"/>
+      <c r="AU8" s="71"/>
+      <c r="AV8" s="71"/>
+      <c r="AW8" s="71"/>
+      <c r="AX8" s="71"/>
+      <c r="AY8" s="72"/>
+      <c r="AZ8" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="BA8" s="80"/>
-      <c r="BB8" s="80"/>
-      <c r="BC8" s="80"/>
-      <c r="BD8" s="80"/>
-      <c r="BE8" s="80"/>
-      <c r="BF8" s="80"/>
-      <c r="BG8" s="80"/>
-      <c r="BH8" s="80"/>
-      <c r="BI8" s="80"/>
-      <c r="BJ8" s="80"/>
-      <c r="BK8" s="80"/>
-      <c r="BL8" s="80"/>
-      <c r="BM8" s="80"/>
-      <c r="BN8" s="80"/>
-      <c r="BO8" s="80"/>
-      <c r="BP8" s="80"/>
-      <c r="BQ8" s="80"/>
-      <c r="BR8" s="80"/>
-      <c r="BS8" s="80"/>
-      <c r="BT8" s="80"/>
-      <c r="BU8" s="80"/>
-      <c r="BV8" s="80"/>
-      <c r="BW8" s="80"/>
-      <c r="BX8" s="80"/>
-      <c r="BY8" s="80"/>
-      <c r="BZ8" s="80"/>
-      <c r="CA8" s="80"/>
-      <c r="CB8" s="80"/>
-      <c r="CC8" s="80"/>
-      <c r="CD8" s="80"/>
-      <c r="CE8" s="80"/>
-      <c r="CF8" s="80"/>
-      <c r="CG8" s="80"/>
-      <c r="CH8" s="80"/>
-      <c r="CI8" s="80"/>
-      <c r="CJ8" s="80"/>
-      <c r="CK8" s="80"/>
-      <c r="CL8" s="80"/>
-      <c r="CM8" s="80"/>
-      <c r="CN8" s="80"/>
-      <c r="CO8" s="80"/>
-      <c r="CP8" s="80"/>
-      <c r="CQ8" s="81"/>
-      <c r="CR8" s="79" t="s">
+      <c r="BA8" s="71"/>
+      <c r="BB8" s="71"/>
+      <c r="BC8" s="71"/>
+      <c r="BD8" s="71"/>
+      <c r="BE8" s="71"/>
+      <c r="BF8" s="71"/>
+      <c r="BG8" s="71"/>
+      <c r="BH8" s="71"/>
+      <c r="BI8" s="71"/>
+      <c r="BJ8" s="71"/>
+      <c r="BK8" s="71"/>
+      <c r="BL8" s="71"/>
+      <c r="BM8" s="71"/>
+      <c r="BN8" s="71"/>
+      <c r="BO8" s="71"/>
+      <c r="BP8" s="71"/>
+      <c r="BQ8" s="71"/>
+      <c r="BR8" s="71"/>
+      <c r="BS8" s="71"/>
+      <c r="BT8" s="71"/>
+      <c r="BU8" s="71"/>
+      <c r="BV8" s="71"/>
+      <c r="BW8" s="71"/>
+      <c r="BX8" s="71"/>
+      <c r="BY8" s="71"/>
+      <c r="BZ8" s="71"/>
+      <c r="CA8" s="71"/>
+      <c r="CB8" s="71"/>
+      <c r="CC8" s="71"/>
+      <c r="CD8" s="71"/>
+      <c r="CE8" s="71"/>
+      <c r="CF8" s="71"/>
+      <c r="CG8" s="71"/>
+      <c r="CH8" s="71"/>
+      <c r="CI8" s="71"/>
+      <c r="CJ8" s="71"/>
+      <c r="CK8" s="71"/>
+      <c r="CL8" s="71"/>
+      <c r="CM8" s="71"/>
+      <c r="CN8" s="71"/>
+      <c r="CO8" s="71"/>
+      <c r="CP8" s="71"/>
+      <c r="CQ8" s="72"/>
+      <c r="CR8" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="CS8" s="80"/>
-      <c r="CT8" s="80"/>
-      <c r="CU8" s="80"/>
-      <c r="CV8" s="80"/>
-      <c r="CW8" s="80"/>
-      <c r="CX8" s="80"/>
-      <c r="CY8" s="80"/>
-      <c r="CZ8" s="80"/>
-      <c r="DA8" s="80"/>
-      <c r="DB8" s="80"/>
-      <c r="DC8" s="80"/>
-      <c r="DD8" s="80"/>
-      <c r="DE8" s="80"/>
-      <c r="DF8" s="80"/>
-      <c r="DG8" s="80"/>
-      <c r="DH8" s="80"/>
-      <c r="DI8" s="80"/>
-      <c r="DJ8" s="80"/>
-      <c r="DK8" s="80"/>
-      <c r="DL8" s="80"/>
-      <c r="DM8" s="80"/>
-      <c r="DN8" s="80"/>
-      <c r="DO8" s="80"/>
-      <c r="DP8" s="80"/>
-      <c r="DQ8" s="80"/>
-      <c r="DR8" s="80"/>
-      <c r="DS8" s="80"/>
-      <c r="DT8" s="80"/>
-      <c r="DU8" s="80"/>
-      <c r="DV8" s="80"/>
-      <c r="DW8" s="80"/>
-      <c r="DX8" s="80"/>
-      <c r="DY8" s="80"/>
-      <c r="DZ8" s="80"/>
-      <c r="EA8" s="80"/>
-      <c r="EB8" s="80"/>
-      <c r="EC8" s="80"/>
-      <c r="ED8" s="80"/>
-      <c r="EE8" s="80"/>
-      <c r="EF8" s="80"/>
-      <c r="EG8" s="80"/>
-      <c r="EH8" s="80"/>
-      <c r="EI8" s="81"/>
-      <c r="EJ8" s="79" t="s">
+      <c r="CS8" s="71"/>
+      <c r="CT8" s="71"/>
+      <c r="CU8" s="71"/>
+      <c r="CV8" s="71"/>
+      <c r="CW8" s="71"/>
+      <c r="CX8" s="71"/>
+      <c r="CY8" s="71"/>
+      <c r="CZ8" s="71"/>
+      <c r="DA8" s="71"/>
+      <c r="DB8" s="71"/>
+      <c r="DC8" s="71"/>
+      <c r="DD8" s="71"/>
+      <c r="DE8" s="71"/>
+      <c r="DF8" s="71"/>
+      <c r="DG8" s="71"/>
+      <c r="DH8" s="71"/>
+      <c r="DI8" s="71"/>
+      <c r="DJ8" s="71"/>
+      <c r="DK8" s="71"/>
+      <c r="DL8" s="71"/>
+      <c r="DM8" s="71"/>
+      <c r="DN8" s="71"/>
+      <c r="DO8" s="71"/>
+      <c r="DP8" s="71"/>
+      <c r="DQ8" s="71"/>
+      <c r="DR8" s="71"/>
+      <c r="DS8" s="71"/>
+      <c r="DT8" s="71"/>
+      <c r="DU8" s="71"/>
+      <c r="DV8" s="71"/>
+      <c r="DW8" s="71"/>
+      <c r="DX8" s="71"/>
+      <c r="DY8" s="71"/>
+      <c r="DZ8" s="71"/>
+      <c r="EA8" s="71"/>
+      <c r="EB8" s="71"/>
+      <c r="EC8" s="71"/>
+      <c r="ED8" s="71"/>
+      <c r="EE8" s="71"/>
+      <c r="EF8" s="71"/>
+      <c r="EG8" s="71"/>
+      <c r="EH8" s="71"/>
+      <c r="EI8" s="72"/>
+      <c r="EJ8" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="EK8" s="80"/>
-      <c r="EL8" s="80"/>
-      <c r="EM8" s="80"/>
-      <c r="EN8" s="80"/>
-      <c r="EO8" s="80"/>
-      <c r="EP8" s="80"/>
-      <c r="EQ8" s="80"/>
-      <c r="ER8" s="80"/>
-      <c r="ES8" s="80"/>
-      <c r="ET8" s="80"/>
-      <c r="EU8" s="80"/>
-      <c r="EV8" s="80"/>
-      <c r="EW8" s="80"/>
-      <c r="EX8" s="80"/>
-      <c r="EY8" s="80"/>
-      <c r="EZ8" s="80"/>
-      <c r="FA8" s="80"/>
-      <c r="FB8" s="80"/>
-      <c r="FC8" s="80"/>
-      <c r="FD8" s="80"/>
-      <c r="FE8" s="80"/>
-      <c r="FF8" s="80"/>
-      <c r="FG8" s="80"/>
-      <c r="FH8" s="80"/>
-      <c r="FI8" s="80"/>
-      <c r="FJ8" s="80"/>
-      <c r="FK8" s="80"/>
-      <c r="FL8" s="80"/>
-      <c r="FM8" s="80"/>
-      <c r="FN8" s="80"/>
-      <c r="FO8" s="80"/>
-      <c r="FP8" s="80"/>
-      <c r="FQ8" s="80"/>
-      <c r="FR8" s="80"/>
-      <c r="FS8" s="80"/>
-      <c r="FT8" s="80"/>
-      <c r="FU8" s="80"/>
-      <c r="FV8" s="80"/>
-      <c r="FW8" s="80"/>
-      <c r="FX8" s="80"/>
-      <c r="FY8" s="80"/>
-      <c r="FZ8" s="80"/>
-      <c r="GA8" s="81"/>
+      <c r="EK8" s="71"/>
+      <c r="EL8" s="71"/>
+      <c r="EM8" s="71"/>
+      <c r="EN8" s="71"/>
+      <c r="EO8" s="71"/>
+      <c r="EP8" s="71"/>
+      <c r="EQ8" s="71"/>
+      <c r="ER8" s="71"/>
+      <c r="ES8" s="71"/>
+      <c r="ET8" s="71"/>
+      <c r="EU8" s="71"/>
+      <c r="EV8" s="71"/>
+      <c r="EW8" s="71"/>
+      <c r="EX8" s="71"/>
+      <c r="EY8" s="71"/>
+      <c r="EZ8" s="71"/>
+      <c r="FA8" s="71"/>
+      <c r="FB8" s="71"/>
+      <c r="FC8" s="71"/>
+      <c r="FD8" s="71"/>
+      <c r="FE8" s="71"/>
+      <c r="FF8" s="71"/>
+      <c r="FG8" s="71"/>
+      <c r="FH8" s="71"/>
+      <c r="FI8" s="71"/>
+      <c r="FJ8" s="71"/>
+      <c r="FK8" s="71"/>
+      <c r="FL8" s="71"/>
+      <c r="FM8" s="71"/>
+      <c r="FN8" s="71"/>
+      <c r="FO8" s="71"/>
+      <c r="FP8" s="71"/>
+      <c r="FQ8" s="71"/>
+      <c r="FR8" s="71"/>
+      <c r="FS8" s="71"/>
+      <c r="FT8" s="71"/>
+      <c r="FU8" s="71"/>
+      <c r="FV8" s="71"/>
+      <c r="FW8" s="71"/>
+      <c r="FX8" s="71"/>
+      <c r="FY8" s="71"/>
+      <c r="FZ8" s="71"/>
+      <c r="GA8" s="72"/>
     </row>
     <row r="9" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="H9" s="79" t="s">
+      <c r="H9" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
-      <c r="K9" s="80"/>
-      <c r="L9" s="80"/>
-      <c r="M9" s="80"/>
-      <c r="N9" s="80"/>
-      <c r="O9" s="80"/>
-      <c r="P9" s="80"/>
-      <c r="Q9" s="80"/>
-      <c r="R9" s="80"/>
-      <c r="S9" s="80"/>
-      <c r="T9" s="80"/>
-      <c r="U9" s="80"/>
-      <c r="V9" s="80"/>
-      <c r="W9" s="80"/>
-      <c r="X9" s="80"/>
-      <c r="Y9" s="80"/>
-      <c r="Z9" s="80"/>
-      <c r="AA9" s="80"/>
-      <c r="AB9" s="80"/>
-      <c r="AC9" s="80"/>
-      <c r="AD9" s="80"/>
-      <c r="AE9" s="80"/>
-      <c r="AF9" s="80"/>
-      <c r="AG9" s="80"/>
-      <c r="AH9" s="80"/>
-      <c r="AI9" s="80"/>
-      <c r="AJ9" s="80"/>
-      <c r="AK9" s="80"/>
-      <c r="AL9" s="80"/>
-      <c r="AM9" s="80"/>
-      <c r="AN9" s="80"/>
-      <c r="AO9" s="80"/>
-      <c r="AP9" s="80"/>
-      <c r="AQ9" s="80"/>
-      <c r="AR9" s="80"/>
-      <c r="AS9" s="80"/>
-      <c r="AT9" s="80"/>
-      <c r="AU9" s="80"/>
-      <c r="AV9" s="80"/>
-      <c r="AW9" s="80"/>
-      <c r="AX9" s="80"/>
-      <c r="AY9" s="81"/>
-      <c r="AZ9" s="79" t="s">
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="71"/>
+      <c r="AE9" s="71"/>
+      <c r="AF9" s="71"/>
+      <c r="AG9" s="71"/>
+      <c r="AH9" s="71"/>
+      <c r="AI9" s="71"/>
+      <c r="AJ9" s="71"/>
+      <c r="AK9" s="71"/>
+      <c r="AL9" s="71"/>
+      <c r="AM9" s="71"/>
+      <c r="AN9" s="71"/>
+      <c r="AO9" s="71"/>
+      <c r="AP9" s="71"/>
+      <c r="AQ9" s="71"/>
+      <c r="AR9" s="71"/>
+      <c r="AS9" s="71"/>
+      <c r="AT9" s="71"/>
+      <c r="AU9" s="71"/>
+      <c r="AV9" s="71"/>
+      <c r="AW9" s="71"/>
+      <c r="AX9" s="71"/>
+      <c r="AY9" s="72"/>
+      <c r="AZ9" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="BA9" s="80"/>
-      <c r="BB9" s="80"/>
-      <c r="BC9" s="80"/>
-      <c r="BD9" s="80"/>
-      <c r="BE9" s="80"/>
-      <c r="BF9" s="80"/>
-      <c r="BG9" s="80"/>
-      <c r="BH9" s="80"/>
-      <c r="BI9" s="80"/>
-      <c r="BJ9" s="80"/>
-      <c r="BK9" s="80"/>
-      <c r="BL9" s="80"/>
-      <c r="BM9" s="80"/>
-      <c r="BN9" s="80"/>
-      <c r="BO9" s="80"/>
-      <c r="BP9" s="80"/>
-      <c r="BQ9" s="80"/>
-      <c r="BR9" s="80"/>
-      <c r="BS9" s="80"/>
-      <c r="BT9" s="80"/>
-      <c r="BU9" s="80"/>
-      <c r="BV9" s="80"/>
-      <c r="BW9" s="80"/>
-      <c r="BX9" s="80"/>
-      <c r="BY9" s="80"/>
-      <c r="BZ9" s="80"/>
-      <c r="CA9" s="80"/>
-      <c r="CB9" s="80"/>
-      <c r="CC9" s="80"/>
-      <c r="CD9" s="80"/>
-      <c r="CE9" s="80"/>
-      <c r="CF9" s="80"/>
-      <c r="CG9" s="80"/>
-      <c r="CH9" s="80"/>
-      <c r="CI9" s="80"/>
-      <c r="CJ9" s="80"/>
-      <c r="CK9" s="80"/>
-      <c r="CL9" s="80"/>
-      <c r="CM9" s="80"/>
-      <c r="CN9" s="80"/>
-      <c r="CO9" s="80"/>
-      <c r="CP9" s="80"/>
-      <c r="CQ9" s="81"/>
-      <c r="CR9" s="79" t="s">
+      <c r="BA9" s="71"/>
+      <c r="BB9" s="71"/>
+      <c r="BC9" s="71"/>
+      <c r="BD9" s="71"/>
+      <c r="BE9" s="71"/>
+      <c r="BF9" s="71"/>
+      <c r="BG9" s="71"/>
+      <c r="BH9" s="71"/>
+      <c r="BI9" s="71"/>
+      <c r="BJ9" s="71"/>
+      <c r="BK9" s="71"/>
+      <c r="BL9" s="71"/>
+      <c r="BM9" s="71"/>
+      <c r="BN9" s="71"/>
+      <c r="BO9" s="71"/>
+      <c r="BP9" s="71"/>
+      <c r="BQ9" s="71"/>
+      <c r="BR9" s="71"/>
+      <c r="BS9" s="71"/>
+      <c r="BT9" s="71"/>
+      <c r="BU9" s="71"/>
+      <c r="BV9" s="71"/>
+      <c r="BW9" s="71"/>
+      <c r="BX9" s="71"/>
+      <c r="BY9" s="71"/>
+      <c r="BZ9" s="71"/>
+      <c r="CA9" s="71"/>
+      <c r="CB9" s="71"/>
+      <c r="CC9" s="71"/>
+      <c r="CD9" s="71"/>
+      <c r="CE9" s="71"/>
+      <c r="CF9" s="71"/>
+      <c r="CG9" s="71"/>
+      <c r="CH9" s="71"/>
+      <c r="CI9" s="71"/>
+      <c r="CJ9" s="71"/>
+      <c r="CK9" s="71"/>
+      <c r="CL9" s="71"/>
+      <c r="CM9" s="71"/>
+      <c r="CN9" s="71"/>
+      <c r="CO9" s="71"/>
+      <c r="CP9" s="71"/>
+      <c r="CQ9" s="72"/>
+      <c r="CR9" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="CS9" s="80"/>
-      <c r="CT9" s="80"/>
-      <c r="CU9" s="80"/>
-      <c r="CV9" s="80"/>
-      <c r="CW9" s="80"/>
-      <c r="CX9" s="80"/>
-      <c r="CY9" s="80"/>
-      <c r="CZ9" s="80"/>
-      <c r="DA9" s="80"/>
-      <c r="DB9" s="80"/>
-      <c r="DC9" s="80"/>
-      <c r="DD9" s="80"/>
-      <c r="DE9" s="80"/>
-      <c r="DF9" s="80"/>
-      <c r="DG9" s="80"/>
-      <c r="DH9" s="80"/>
-      <c r="DI9" s="80"/>
-      <c r="DJ9" s="80"/>
-      <c r="DK9" s="80"/>
-      <c r="DL9" s="80"/>
-      <c r="DM9" s="80"/>
-      <c r="DN9" s="80"/>
-      <c r="DO9" s="80"/>
-      <c r="DP9" s="80"/>
-      <c r="DQ9" s="80"/>
-      <c r="DR9" s="80"/>
-      <c r="DS9" s="80"/>
-      <c r="DT9" s="80"/>
-      <c r="DU9" s="80"/>
-      <c r="DV9" s="80"/>
-      <c r="DW9" s="80"/>
-      <c r="DX9" s="80"/>
-      <c r="DY9" s="80"/>
-      <c r="DZ9" s="80"/>
-      <c r="EA9" s="80"/>
-      <c r="EB9" s="80"/>
-      <c r="EC9" s="80"/>
-      <c r="ED9" s="80"/>
-      <c r="EE9" s="80"/>
-      <c r="EF9" s="80"/>
-      <c r="EG9" s="80"/>
-      <c r="EH9" s="80"/>
-      <c r="EI9" s="81"/>
-      <c r="EJ9" s="79" t="s">
+      <c r="CS9" s="71"/>
+      <c r="CT9" s="71"/>
+      <c r="CU9" s="71"/>
+      <c r="CV9" s="71"/>
+      <c r="CW9" s="71"/>
+      <c r="CX9" s="71"/>
+      <c r="CY9" s="71"/>
+      <c r="CZ9" s="71"/>
+      <c r="DA9" s="71"/>
+      <c r="DB9" s="71"/>
+      <c r="DC9" s="71"/>
+      <c r="DD9" s="71"/>
+      <c r="DE9" s="71"/>
+      <c r="DF9" s="71"/>
+      <c r="DG9" s="71"/>
+      <c r="DH9" s="71"/>
+      <c r="DI9" s="71"/>
+      <c r="DJ9" s="71"/>
+      <c r="DK9" s="71"/>
+      <c r="DL9" s="71"/>
+      <c r="DM9" s="71"/>
+      <c r="DN9" s="71"/>
+      <c r="DO9" s="71"/>
+      <c r="DP9" s="71"/>
+      <c r="DQ9" s="71"/>
+      <c r="DR9" s="71"/>
+      <c r="DS9" s="71"/>
+      <c r="DT9" s="71"/>
+      <c r="DU9" s="71"/>
+      <c r="DV9" s="71"/>
+      <c r="DW9" s="71"/>
+      <c r="DX9" s="71"/>
+      <c r="DY9" s="71"/>
+      <c r="DZ9" s="71"/>
+      <c r="EA9" s="71"/>
+      <c r="EB9" s="71"/>
+      <c r="EC9" s="71"/>
+      <c r="ED9" s="71"/>
+      <c r="EE9" s="71"/>
+      <c r="EF9" s="71"/>
+      <c r="EG9" s="71"/>
+      <c r="EH9" s="71"/>
+      <c r="EI9" s="72"/>
+      <c r="EJ9" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="EK9" s="80"/>
-      <c r="EL9" s="80"/>
-      <c r="EM9" s="80"/>
-      <c r="EN9" s="80"/>
-      <c r="EO9" s="80"/>
-      <c r="EP9" s="80"/>
-      <c r="EQ9" s="80"/>
-      <c r="ER9" s="80"/>
-      <c r="ES9" s="80"/>
-      <c r="ET9" s="80"/>
-      <c r="EU9" s="80"/>
-      <c r="EV9" s="80"/>
-      <c r="EW9" s="80"/>
-      <c r="EX9" s="80"/>
-      <c r="EY9" s="80"/>
-      <c r="EZ9" s="80"/>
-      <c r="FA9" s="80"/>
-      <c r="FB9" s="80"/>
-      <c r="FC9" s="80"/>
-      <c r="FD9" s="80"/>
-      <c r="FE9" s="80"/>
-      <c r="FF9" s="80"/>
-      <c r="FG9" s="80"/>
-      <c r="FH9" s="80"/>
-      <c r="FI9" s="80"/>
-      <c r="FJ9" s="80"/>
-      <c r="FK9" s="80"/>
-      <c r="FL9" s="80"/>
-      <c r="FM9" s="80"/>
-      <c r="FN9" s="80"/>
-      <c r="FO9" s="80"/>
-      <c r="FP9" s="80"/>
-      <c r="FQ9" s="80"/>
-      <c r="FR9" s="80"/>
-      <c r="FS9" s="80"/>
-      <c r="FT9" s="80"/>
-      <c r="FU9" s="80"/>
-      <c r="FV9" s="80"/>
-      <c r="FW9" s="80"/>
-      <c r="FX9" s="80"/>
-      <c r="FY9" s="80"/>
-      <c r="FZ9" s="80"/>
-      <c r="GA9" s="81"/>
+      <c r="EK9" s="71"/>
+      <c r="EL9" s="71"/>
+      <c r="EM9" s="71"/>
+      <c r="EN9" s="71"/>
+      <c r="EO9" s="71"/>
+      <c r="EP9" s="71"/>
+      <c r="EQ9" s="71"/>
+      <c r="ER9" s="71"/>
+      <c r="ES9" s="71"/>
+      <c r="ET9" s="71"/>
+      <c r="EU9" s="71"/>
+      <c r="EV9" s="71"/>
+      <c r="EW9" s="71"/>
+      <c r="EX9" s="71"/>
+      <c r="EY9" s="71"/>
+      <c r="EZ9" s="71"/>
+      <c r="FA9" s="71"/>
+      <c r="FB9" s="71"/>
+      <c r="FC9" s="71"/>
+      <c r="FD9" s="71"/>
+      <c r="FE9" s="71"/>
+      <c r="FF9" s="71"/>
+      <c r="FG9" s="71"/>
+      <c r="FH9" s="71"/>
+      <c r="FI9" s="71"/>
+      <c r="FJ9" s="71"/>
+      <c r="FK9" s="71"/>
+      <c r="FL9" s="71"/>
+      <c r="FM9" s="71"/>
+      <c r="FN9" s="71"/>
+      <c r="FO9" s="71"/>
+      <c r="FP9" s="71"/>
+      <c r="FQ9" s="71"/>
+      <c r="FR9" s="71"/>
+      <c r="FS9" s="71"/>
+      <c r="FT9" s="71"/>
+      <c r="FU9" s="71"/>
+      <c r="FV9" s="71"/>
+      <c r="FW9" s="71"/>
+      <c r="FX9" s="71"/>
+      <c r="FY9" s="71"/>
+      <c r="FZ9" s="71"/>
+      <c r="GA9" s="72"/>
     </row>
     <row r="10" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="72"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
       <c r="H10" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="I10" s="102" t="s">
+      <c r="I10" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="102"/>
-      <c r="S10" s="102"/>
-      <c r="T10" s="102" t="s">
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="U10" s="102"/>
-      <c r="V10" s="102"/>
-      <c r="W10" s="102"/>
-      <c r="X10" s="102"/>
-      <c r="Y10" s="102"/>
-      <c r="Z10" s="102"/>
-      <c r="AA10" s="102"/>
-      <c r="AB10" s="102"/>
-      <c r="AC10" s="102"/>
-      <c r="AD10" s="102"/>
-      <c r="AE10" s="103" t="s">
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="67"/>
+      <c r="AA10" s="67"/>
+      <c r="AB10" s="67"/>
+      <c r="AC10" s="67"/>
+      <c r="AD10" s="67"/>
+      <c r="AE10" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="AF10" s="103"/>
-      <c r="AG10" s="103"/>
-      <c r="AH10" s="103" t="s">
+      <c r="AF10" s="68"/>
+      <c r="AG10" s="68"/>
+      <c r="AH10" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="AI10" s="103"/>
-      <c r="AJ10" s="103"/>
-      <c r="AK10" s="103"/>
-      <c r="AL10" s="103" t="s">
+      <c r="AI10" s="68"/>
+      <c r="AJ10" s="68"/>
+      <c r="AK10" s="68"/>
+      <c r="AL10" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="AM10" s="103"/>
-      <c r="AN10" s="103"/>
-      <c r="AO10" s="103"/>
-      <c r="AP10" s="70" t="s">
+      <c r="AM10" s="68"/>
+      <c r="AN10" s="68"/>
+      <c r="AO10" s="68"/>
+      <c r="AP10" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="AQ10" s="71"/>
-      <c r="AR10" s="71"/>
-      <c r="AS10" s="71"/>
-      <c r="AT10" s="71"/>
-      <c r="AU10" s="71"/>
-      <c r="AV10" s="71"/>
-      <c r="AW10" s="71"/>
-      <c r="AX10" s="71"/>
-      <c r="AY10" s="72"/>
+      <c r="AQ10" s="65"/>
+      <c r="AR10" s="65"/>
+      <c r="AS10" s="65"/>
+      <c r="AT10" s="65"/>
+      <c r="AU10" s="65"/>
+      <c r="AV10" s="65"/>
+      <c r="AW10" s="65"/>
+      <c r="AX10" s="65"/>
+      <c r="AY10" s="66"/>
       <c r="AZ10" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="BA10" s="102" t="s">
+      <c r="BA10" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="BB10" s="102"/>
-      <c r="BC10" s="102"/>
-      <c r="BD10" s="102"/>
-      <c r="BE10" s="102"/>
-      <c r="BF10" s="102"/>
-      <c r="BG10" s="102"/>
-      <c r="BH10" s="102"/>
-      <c r="BI10" s="102"/>
-      <c r="BJ10" s="102"/>
-      <c r="BK10" s="102"/>
-      <c r="BL10" s="102" t="s">
+      <c r="BB10" s="67"/>
+      <c r="BC10" s="67"/>
+      <c r="BD10" s="67"/>
+      <c r="BE10" s="67"/>
+      <c r="BF10" s="67"/>
+      <c r="BG10" s="67"/>
+      <c r="BH10" s="67"/>
+      <c r="BI10" s="67"/>
+      <c r="BJ10" s="67"/>
+      <c r="BK10" s="67"/>
+      <c r="BL10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="BM10" s="102"/>
-      <c r="BN10" s="102"/>
-      <c r="BO10" s="102"/>
-      <c r="BP10" s="102"/>
-      <c r="BQ10" s="102"/>
-      <c r="BR10" s="102"/>
-      <c r="BS10" s="102"/>
-      <c r="BT10" s="102"/>
-      <c r="BU10" s="102"/>
-      <c r="BV10" s="102"/>
-      <c r="BW10" s="103" t="s">
+      <c r="BM10" s="67"/>
+      <c r="BN10" s="67"/>
+      <c r="BO10" s="67"/>
+      <c r="BP10" s="67"/>
+      <c r="BQ10" s="67"/>
+      <c r="BR10" s="67"/>
+      <c r="BS10" s="67"/>
+      <c r="BT10" s="67"/>
+      <c r="BU10" s="67"/>
+      <c r="BV10" s="67"/>
+      <c r="BW10" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="BX10" s="103"/>
-      <c r="BY10" s="103"/>
-      <c r="BZ10" s="103" t="s">
+      <c r="BX10" s="68"/>
+      <c r="BY10" s="68"/>
+      <c r="BZ10" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="CA10" s="103"/>
-      <c r="CB10" s="103"/>
-      <c r="CC10" s="103"/>
-      <c r="CD10" s="103" t="s">
+      <c r="CA10" s="68"/>
+      <c r="CB10" s="68"/>
+      <c r="CC10" s="68"/>
+      <c r="CD10" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="CE10" s="103"/>
-      <c r="CF10" s="103"/>
-      <c r="CG10" s="103"/>
-      <c r="CH10" s="70" t="s">
+      <c r="CE10" s="68"/>
+      <c r="CF10" s="68"/>
+      <c r="CG10" s="68"/>
+      <c r="CH10" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="CI10" s="71"/>
-      <c r="CJ10" s="71"/>
-      <c r="CK10" s="71"/>
-      <c r="CL10" s="71"/>
-      <c r="CM10" s="71"/>
-      <c r="CN10" s="71"/>
-      <c r="CO10" s="71"/>
-      <c r="CP10" s="71"/>
-      <c r="CQ10" s="72"/>
+      <c r="CI10" s="65"/>
+      <c r="CJ10" s="65"/>
+      <c r="CK10" s="65"/>
+      <c r="CL10" s="65"/>
+      <c r="CM10" s="65"/>
+      <c r="CN10" s="65"/>
+      <c r="CO10" s="65"/>
+      <c r="CP10" s="65"/>
+      <c r="CQ10" s="66"/>
       <c r="CR10" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="CS10" s="102" t="s">
+      <c r="CS10" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="CT10" s="102"/>
-      <c r="CU10" s="102"/>
-      <c r="CV10" s="102"/>
-      <c r="CW10" s="102"/>
-      <c r="CX10" s="102"/>
-      <c r="CY10" s="102"/>
-      <c r="CZ10" s="102"/>
-      <c r="DA10" s="102"/>
-      <c r="DB10" s="102"/>
-      <c r="DC10" s="102"/>
-      <c r="DD10" s="102" t="s">
+      <c r="CT10" s="67"/>
+      <c r="CU10" s="67"/>
+      <c r="CV10" s="67"/>
+      <c r="CW10" s="67"/>
+      <c r="CX10" s="67"/>
+      <c r="CY10" s="67"/>
+      <c r="CZ10" s="67"/>
+      <c r="DA10" s="67"/>
+      <c r="DB10" s="67"/>
+      <c r="DC10" s="67"/>
+      <c r="DD10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="DE10" s="102"/>
-      <c r="DF10" s="102"/>
-      <c r="DG10" s="102"/>
-      <c r="DH10" s="102"/>
-      <c r="DI10" s="102"/>
-      <c r="DJ10" s="102"/>
-      <c r="DK10" s="102"/>
-      <c r="DL10" s="102"/>
-      <c r="DM10" s="102"/>
-      <c r="DN10" s="102"/>
-      <c r="DO10" s="103" t="s">
+      <c r="DE10" s="67"/>
+      <c r="DF10" s="67"/>
+      <c r="DG10" s="67"/>
+      <c r="DH10" s="67"/>
+      <c r="DI10" s="67"/>
+      <c r="DJ10" s="67"/>
+      <c r="DK10" s="67"/>
+      <c r="DL10" s="67"/>
+      <c r="DM10" s="67"/>
+      <c r="DN10" s="67"/>
+      <c r="DO10" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="DP10" s="103"/>
-      <c r="DQ10" s="103"/>
-      <c r="DR10" s="103" t="s">
+      <c r="DP10" s="68"/>
+      <c r="DQ10" s="68"/>
+      <c r="DR10" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="DS10" s="103"/>
-      <c r="DT10" s="103"/>
-      <c r="DU10" s="103"/>
-      <c r="DV10" s="103" t="s">
+      <c r="DS10" s="68"/>
+      <c r="DT10" s="68"/>
+      <c r="DU10" s="68"/>
+      <c r="DV10" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="DW10" s="103"/>
-      <c r="DX10" s="103"/>
-      <c r="DY10" s="103"/>
-      <c r="DZ10" s="70" t="s">
+      <c r="DW10" s="68"/>
+      <c r="DX10" s="68"/>
+      <c r="DY10" s="68"/>
+      <c r="DZ10" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="EA10" s="71"/>
-      <c r="EB10" s="71"/>
-      <c r="EC10" s="71"/>
-      <c r="ED10" s="71"/>
-      <c r="EE10" s="71"/>
-      <c r="EF10" s="71"/>
-      <c r="EG10" s="71"/>
-      <c r="EH10" s="71"/>
-      <c r="EI10" s="72"/>
+      <c r="EA10" s="65"/>
+      <c r="EB10" s="65"/>
+      <c r="EC10" s="65"/>
+      <c r="ED10" s="65"/>
+      <c r="EE10" s="65"/>
+      <c r="EF10" s="65"/>
+      <c r="EG10" s="65"/>
+      <c r="EH10" s="65"/>
+      <c r="EI10" s="66"/>
       <c r="EJ10" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="EK10" s="70" t="s">
+      <c r="EK10" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="EL10" s="71"/>
-      <c r="EM10" s="71"/>
-      <c r="EN10" s="71"/>
-      <c r="EO10" s="71"/>
-      <c r="EP10" s="71"/>
-      <c r="EQ10" s="71"/>
-      <c r="ER10" s="71"/>
-      <c r="ES10" s="71"/>
-      <c r="ET10" s="71"/>
-      <c r="EU10" s="72"/>
-      <c r="EV10" s="102" t="s">
+      <c r="EL10" s="65"/>
+      <c r="EM10" s="65"/>
+      <c r="EN10" s="65"/>
+      <c r="EO10" s="65"/>
+      <c r="EP10" s="65"/>
+      <c r="EQ10" s="65"/>
+      <c r="ER10" s="65"/>
+      <c r="ES10" s="65"/>
+      <c r="ET10" s="65"/>
+      <c r="EU10" s="66"/>
+      <c r="EV10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="EW10" s="102"/>
-      <c r="EX10" s="102"/>
-      <c r="EY10" s="102"/>
-      <c r="EZ10" s="102"/>
-      <c r="FA10" s="102"/>
-      <c r="FB10" s="102"/>
-      <c r="FC10" s="102"/>
-      <c r="FD10" s="102"/>
-      <c r="FE10" s="102"/>
-      <c r="FF10" s="102"/>
-      <c r="FG10" s="103" t="s">
+      <c r="EW10" s="67"/>
+      <c r="EX10" s="67"/>
+      <c r="EY10" s="67"/>
+      <c r="EZ10" s="67"/>
+      <c r="FA10" s="67"/>
+      <c r="FB10" s="67"/>
+      <c r="FC10" s="67"/>
+      <c r="FD10" s="67"/>
+      <c r="FE10" s="67"/>
+      <c r="FF10" s="67"/>
+      <c r="FG10" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="FH10" s="103"/>
-      <c r="FI10" s="103"/>
-      <c r="FJ10" s="103" t="s">
+      <c r="FH10" s="68"/>
+      <c r="FI10" s="68"/>
+      <c r="FJ10" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="FK10" s="103"/>
-      <c r="FL10" s="103"/>
-      <c r="FM10" s="103"/>
-      <c r="FN10" s="103" t="s">
+      <c r="FK10" s="68"/>
+      <c r="FL10" s="68"/>
+      <c r="FM10" s="68"/>
+      <c r="FN10" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="FO10" s="103"/>
-      <c r="FP10" s="103"/>
-      <c r="FQ10" s="108"/>
-      <c r="FR10" s="70" t="s">
+      <c r="FO10" s="68"/>
+      <c r="FP10" s="68"/>
+      <c r="FQ10" s="69"/>
+      <c r="FR10" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="FS10" s="71"/>
-      <c r="FT10" s="71"/>
-      <c r="FU10" s="71"/>
-      <c r="FV10" s="71"/>
-      <c r="FW10" s="71"/>
-      <c r="FX10" s="71"/>
-      <c r="FY10" s="71"/>
-      <c r="FZ10" s="71"/>
-      <c r="GA10" s="72"/>
+      <c r="FS10" s="65"/>
+      <c r="FT10" s="65"/>
+      <c r="FU10" s="65"/>
+      <c r="FV10" s="65"/>
+      <c r="FW10" s="65"/>
+      <c r="FX10" s="65"/>
+      <c r="FY10" s="65"/>
+      <c r="FZ10" s="65"/>
+      <c r="GA10" s="66"/>
     </row>
     <row r="11" spans="1:183" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="31" t="s">
@@ -3580,17 +3616,23 @@
       <c r="AB11" s="34"/>
       <c r="AC11" s="34"/>
       <c r="AD11" s="36"/>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="5"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="7"/>
-      <c r="AL11" s="5"/>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="6"/>
-      <c r="AO11" s="7"/>
+      <c r="AE11" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF11" s="110"/>
+      <c r="AG11" s="111"/>
+      <c r="AH11" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI11" s="110"/>
+      <c r="AJ11" s="110"/>
+      <c r="AK11" s="111"/>
+      <c r="AL11" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM11" s="110"/>
+      <c r="AN11" s="110"/>
+      <c r="AO11" s="111"/>
       <c r="AP11" s="31"/>
       <c r="AQ11" s="27"/>
       <c r="AR11" s="27"/>
@@ -3787,17 +3829,17 @@
       <c r="AB12" s="39"/>
       <c r="AC12" s="39"/>
       <c r="AD12" s="41"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="18"/>
-      <c r="AG12" s="18"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="18"/>
-      <c r="AJ12" s="18"/>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="18"/>
-      <c r="AN12" s="18"/>
-      <c r="AO12" s="19"/>
+      <c r="AE12" s="113"/>
+      <c r="AF12" s="114"/>
+      <c r="AG12" s="115"/>
+      <c r="AH12" s="113"/>
+      <c r="AI12" s="114"/>
+      <c r="AJ12" s="114"/>
+      <c r="AK12" s="115"/>
+      <c r="AL12" s="113"/>
+      <c r="AM12" s="114"/>
+      <c r="AN12" s="114"/>
+      <c r="AO12" s="115"/>
       <c r="AP12" s="38"/>
       <c r="AQ12" s="39"/>
       <c r="AR12" s="39"/>
@@ -3984,17 +4026,23 @@
       <c r="AB13" s="27"/>
       <c r="AC13" s="27"/>
       <c r="AD13" s="32"/>
-      <c r="AE13" s="8"/>
-      <c r="AF13" s="9"/>
-      <c r="AG13" s="9"/>
-      <c r="AH13" s="8"/>
-      <c r="AI13" s="9"/>
-      <c r="AJ13" s="9"/>
-      <c r="AK13" s="10"/>
-      <c r="AL13" s="8"/>
-      <c r="AM13" s="9"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="10"/>
+      <c r="AE13" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF13" s="110"/>
+      <c r="AG13" s="111"/>
+      <c r="AH13" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI13" s="110"/>
+      <c r="AJ13" s="110"/>
+      <c r="AK13" s="111"/>
+      <c r="AL13" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM13" s="110"/>
+      <c r="AN13" s="110"/>
+      <c r="AO13" s="111"/>
       <c r="AP13" s="31"/>
       <c r="AQ13" s="27"/>
       <c r="AR13" s="27"/>
@@ -4189,17 +4237,17 @@
       <c r="AB14" s="39"/>
       <c r="AC14" s="39"/>
       <c r="AD14" s="41"/>
-      <c r="AE14" s="8"/>
-      <c r="AF14" s="9"/>
-      <c r="AG14" s="9"/>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="9"/>
-      <c r="AJ14" s="9"/>
-      <c r="AK14" s="10"/>
-      <c r="AL14" s="8"/>
-      <c r="AM14" s="9"/>
-      <c r="AN14" s="9"/>
-      <c r="AO14" s="10"/>
+      <c r="AE14" s="113"/>
+      <c r="AF14" s="114"/>
+      <c r="AG14" s="115"/>
+      <c r="AH14" s="113"/>
+      <c r="AI14" s="114"/>
+      <c r="AJ14" s="114"/>
+      <c r="AK14" s="115"/>
+      <c r="AL14" s="113"/>
+      <c r="AM14" s="114"/>
+      <c r="AN14" s="114"/>
+      <c r="AO14" s="115"/>
       <c r="AP14" s="38"/>
       <c r="AQ14" s="39"/>
       <c r="AR14" s="39"/>
@@ -4386,17 +4434,23 @@
       <c r="AB15" s="27"/>
       <c r="AC15" s="27"/>
       <c r="AD15" s="32"/>
-      <c r="AE15" s="5"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="5"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="7"/>
-      <c r="AL15" s="5"/>
-      <c r="AM15" s="6"/>
-      <c r="AN15" s="6"/>
-      <c r="AO15" s="7"/>
+      <c r="AE15" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF15" s="110"/>
+      <c r="AG15" s="111"/>
+      <c r="AH15" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI15" s="110"/>
+      <c r="AJ15" s="110"/>
+      <c r="AK15" s="111"/>
+      <c r="AL15" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM15" s="110"/>
+      <c r="AN15" s="110"/>
+      <c r="AO15" s="111"/>
       <c r="AP15" s="31"/>
       <c r="AQ15" s="27"/>
       <c r="AR15" s="27"/>
@@ -4593,17 +4647,17 @@
       <c r="AB16" s="27"/>
       <c r="AC16" s="27"/>
       <c r="AD16" s="32"/>
-      <c r="AE16" s="8"/>
-      <c r="AF16" s="9"/>
-      <c r="AG16" s="9"/>
-      <c r="AH16" s="8"/>
-      <c r="AI16" s="9"/>
-      <c r="AJ16" s="9"/>
-      <c r="AK16" s="10"/>
-      <c r="AL16" s="8"/>
-      <c r="AM16" s="9"/>
-      <c r="AN16" s="9"/>
-      <c r="AO16" s="10"/>
+      <c r="AE16" s="116"/>
+      <c r="AF16" s="117"/>
+      <c r="AG16" s="118"/>
+      <c r="AH16" s="116"/>
+      <c r="AI16" s="117"/>
+      <c r="AJ16" s="117"/>
+      <c r="AK16" s="118"/>
+      <c r="AL16" s="116"/>
+      <c r="AM16" s="117"/>
+      <c r="AN16" s="117"/>
+      <c r="AO16" s="118"/>
       <c r="AP16" s="31"/>
       <c r="AQ16" s="27"/>
       <c r="AR16" s="27"/>
@@ -4792,17 +4846,17 @@
       <c r="AB17" s="39"/>
       <c r="AC17" s="39"/>
       <c r="AD17" s="41"/>
-      <c r="AE17" s="17"/>
-      <c r="AF17" s="18"/>
-      <c r="AG17" s="18"/>
-      <c r="AH17" s="17"/>
-      <c r="AI17" s="18"/>
-      <c r="AJ17" s="18"/>
-      <c r="AK17" s="19"/>
-      <c r="AL17" s="17"/>
-      <c r="AM17" s="18"/>
-      <c r="AN17" s="18"/>
-      <c r="AO17" s="19"/>
+      <c r="AE17" s="113"/>
+      <c r="AF17" s="114"/>
+      <c r="AG17" s="115"/>
+      <c r="AH17" s="113"/>
+      <c r="AI17" s="114"/>
+      <c r="AJ17" s="114"/>
+      <c r="AK17" s="115"/>
+      <c r="AL17" s="113"/>
+      <c r="AM17" s="114"/>
+      <c r="AN17" s="114"/>
+      <c r="AO17" s="115"/>
       <c r="AP17" s="38"/>
       <c r="AQ17" s="39"/>
       <c r="AR17" s="39"/>
@@ -4991,17 +5045,23 @@
       <c r="AB18" s="27"/>
       <c r="AC18" s="27"/>
       <c r="AD18" s="32"/>
-      <c r="AE18" s="5"/>
-      <c r="AF18" s="6"/>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="5"/>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="6"/>
-      <c r="AK18" s="7"/>
-      <c r="AL18" s="5"/>
-      <c r="AM18" s="6"/>
-      <c r="AN18" s="6"/>
-      <c r="AO18" s="7"/>
+      <c r="AE18" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF18" s="110"/>
+      <c r="AG18" s="111"/>
+      <c r="AH18" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI18" s="110"/>
+      <c r="AJ18" s="110"/>
+      <c r="AK18" s="111"/>
+      <c r="AL18" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM18" s="110"/>
+      <c r="AN18" s="110"/>
+      <c r="AO18" s="111"/>
       <c r="AP18" s="31"/>
       <c r="AQ18" s="27"/>
       <c r="AR18" s="27"/>
@@ -5198,17 +5258,17 @@
       <c r="AB19" s="27"/>
       <c r="AC19" s="27"/>
       <c r="AD19" s="32"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="20"/>
-      <c r="AG19" s="20"/>
-      <c r="AH19" s="2"/>
-      <c r="AI19" s="20"/>
-      <c r="AJ19" s="20"/>
-      <c r="AK19" s="4"/>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="20"/>
-      <c r="AN19" s="20"/>
-      <c r="AO19" s="4"/>
+      <c r="AE19" s="116"/>
+      <c r="AF19" s="117"/>
+      <c r="AG19" s="118"/>
+      <c r="AH19" s="116"/>
+      <c r="AI19" s="117"/>
+      <c r="AJ19" s="117"/>
+      <c r="AK19" s="118"/>
+      <c r="AL19" s="116"/>
+      <c r="AM19" s="117"/>
+      <c r="AN19" s="117"/>
+      <c r="AO19" s="118"/>
       <c r="AP19" s="31"/>
       <c r="AQ19" s="27"/>
       <c r="AR19" s="27"/>
@@ -5397,17 +5457,17 @@
       <c r="AB20" s="39"/>
       <c r="AC20" s="39"/>
       <c r="AD20" s="41"/>
-      <c r="AE20" s="14"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15"/>
-      <c r="AH20" s="14"/>
-      <c r="AI20" s="15"/>
-      <c r="AJ20" s="15"/>
-      <c r="AK20" s="16"/>
-      <c r="AL20" s="14"/>
-      <c r="AM20" s="15"/>
-      <c r="AN20" s="15"/>
-      <c r="AO20" s="16"/>
+      <c r="AE20" s="113"/>
+      <c r="AF20" s="114"/>
+      <c r="AG20" s="115"/>
+      <c r="AH20" s="113"/>
+      <c r="AI20" s="114"/>
+      <c r="AJ20" s="114"/>
+      <c r="AK20" s="115"/>
+      <c r="AL20" s="113"/>
+      <c r="AM20" s="114"/>
+      <c r="AN20" s="114"/>
+      <c r="AO20" s="115"/>
       <c r="AP20" s="38"/>
       <c r="AQ20" s="39"/>
       <c r="AR20" s="39"/>
@@ -5594,17 +5654,23 @@
       <c r="AB21" s="27"/>
       <c r="AC21" s="27"/>
       <c r="AD21" s="32"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="2"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="3"/>
-      <c r="AK21" s="4"/>
-      <c r="AL21" s="2"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="3"/>
-      <c r="AO21" s="4"/>
+      <c r="AE21" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF21" s="110"/>
+      <c r="AG21" s="111"/>
+      <c r="AH21" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI21" s="110"/>
+      <c r="AJ21" s="110"/>
+      <c r="AK21" s="111"/>
+      <c r="AL21" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM21" s="110"/>
+      <c r="AN21" s="110"/>
+      <c r="AO21" s="111"/>
       <c r="AP21" s="31"/>
       <c r="AQ21" s="27"/>
       <c r="AR21" s="27"/>
@@ -5801,17 +5867,17 @@
       <c r="AB22" s="27"/>
       <c r="AC22" s="27"/>
       <c r="AD22" s="32"/>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="20"/>
-      <c r="AG22" s="20"/>
-      <c r="AH22" s="2"/>
-      <c r="AI22" s="20"/>
-      <c r="AJ22" s="20"/>
-      <c r="AK22" s="4"/>
-      <c r="AL22" s="2"/>
-      <c r="AM22" s="20"/>
-      <c r="AN22" s="20"/>
-      <c r="AO22" s="4"/>
+      <c r="AE22" s="116"/>
+      <c r="AF22" s="117"/>
+      <c r="AG22" s="118"/>
+      <c r="AH22" s="116"/>
+      <c r="AI22" s="117"/>
+      <c r="AJ22" s="117"/>
+      <c r="AK22" s="118"/>
+      <c r="AL22" s="116"/>
+      <c r="AM22" s="117"/>
+      <c r="AN22" s="117"/>
+      <c r="AO22" s="118"/>
       <c r="AP22" s="31"/>
       <c r="AQ22" s="27"/>
       <c r="AR22" s="27"/>
@@ -6000,17 +6066,17 @@
       <c r="AB23" s="39"/>
       <c r="AC23" s="39"/>
       <c r="AD23" s="41"/>
-      <c r="AE23" s="14"/>
-      <c r="AF23" s="15"/>
-      <c r="AG23" s="15"/>
-      <c r="AH23" s="14"/>
-      <c r="AI23" s="15"/>
-      <c r="AJ23" s="15"/>
-      <c r="AK23" s="16"/>
-      <c r="AL23" s="14"/>
-      <c r="AM23" s="15"/>
-      <c r="AN23" s="15"/>
-      <c r="AO23" s="16"/>
+      <c r="AE23" s="113"/>
+      <c r="AF23" s="114"/>
+      <c r="AG23" s="115"/>
+      <c r="AH23" s="113"/>
+      <c r="AI23" s="114"/>
+      <c r="AJ23" s="114"/>
+      <c r="AK23" s="115"/>
+      <c r="AL23" s="113"/>
+      <c r="AM23" s="114"/>
+      <c r="AN23" s="114"/>
+      <c r="AO23" s="115"/>
       <c r="AP23" s="38"/>
       <c r="AQ23" s="39"/>
       <c r="AR23" s="39"/>
@@ -6197,17 +6263,23 @@
       <c r="AB24" s="27"/>
       <c r="AC24" s="27"/>
       <c r="AD24" s="32"/>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="3"/>
-      <c r="AG24" s="3"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="3"/>
-      <c r="AJ24" s="3"/>
-      <c r="AK24" s="4"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="3"/>
-      <c r="AN24" s="3"/>
-      <c r="AO24" s="4"/>
+      <c r="AE24" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF24" s="110"/>
+      <c r="AG24" s="111"/>
+      <c r="AH24" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI24" s="110"/>
+      <c r="AJ24" s="110"/>
+      <c r="AK24" s="111"/>
+      <c r="AL24" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM24" s="110"/>
+      <c r="AN24" s="110"/>
+      <c r="AO24" s="111"/>
       <c r="AP24" s="31"/>
       <c r="AQ24" s="27"/>
       <c r="AR24" s="27"/>
@@ -6404,17 +6476,17 @@
       <c r="AB25" s="27"/>
       <c r="AC25" s="27"/>
       <c r="AD25" s="32"/>
-      <c r="AE25" s="2"/>
-      <c r="AF25" s="3"/>
-      <c r="AG25" s="3"/>
-      <c r="AH25" s="2"/>
-      <c r="AI25" s="3"/>
-      <c r="AJ25" s="3"/>
-      <c r="AK25" s="4"/>
-      <c r="AL25" s="2"/>
-      <c r="AM25" s="3"/>
-      <c r="AN25" s="3"/>
-      <c r="AO25" s="4"/>
+      <c r="AE25" s="116"/>
+      <c r="AF25" s="117"/>
+      <c r="AG25" s="118"/>
+      <c r="AH25" s="116"/>
+      <c r="AI25" s="117"/>
+      <c r="AJ25" s="117"/>
+      <c r="AK25" s="118"/>
+      <c r="AL25" s="116"/>
+      <c r="AM25" s="117"/>
+      <c r="AN25" s="117"/>
+      <c r="AO25" s="118"/>
       <c r="AP25" s="31"/>
       <c r="AQ25" s="27"/>
       <c r="AR25" s="27"/>
@@ -6603,17 +6675,17 @@
       <c r="AB26" s="27"/>
       <c r="AC26" s="27"/>
       <c r="AD26" s="32"/>
-      <c r="AE26" s="2"/>
-      <c r="AF26" s="20"/>
-      <c r="AG26" s="20"/>
-      <c r="AH26" s="2"/>
-      <c r="AI26" s="20"/>
-      <c r="AJ26" s="20"/>
-      <c r="AK26" s="4"/>
-      <c r="AL26" s="2"/>
-      <c r="AM26" s="20"/>
-      <c r="AN26" s="20"/>
-      <c r="AO26" s="4"/>
+      <c r="AE26" s="116"/>
+      <c r="AF26" s="117"/>
+      <c r="AG26" s="118"/>
+      <c r="AH26" s="116"/>
+      <c r="AI26" s="117"/>
+      <c r="AJ26" s="117"/>
+      <c r="AK26" s="118"/>
+      <c r="AL26" s="116"/>
+      <c r="AM26" s="117"/>
+      <c r="AN26" s="117"/>
+      <c r="AO26" s="118"/>
       <c r="AP26" s="31"/>
       <c r="AQ26" s="27"/>
       <c r="AR26" s="27"/>
@@ -6796,17 +6868,17 @@
       <c r="AB27" s="27"/>
       <c r="AC27" s="27"/>
       <c r="AD27" s="32"/>
-      <c r="AE27" s="2"/>
-      <c r="AF27" s="20"/>
-      <c r="AG27" s="20"/>
-      <c r="AH27" s="2"/>
-      <c r="AI27" s="20"/>
-      <c r="AJ27" s="20"/>
-      <c r="AK27" s="4"/>
-      <c r="AL27" s="2"/>
-      <c r="AM27" s="20"/>
-      <c r="AN27" s="20"/>
-      <c r="AO27" s="4"/>
+      <c r="AE27" s="116"/>
+      <c r="AF27" s="117"/>
+      <c r="AG27" s="118"/>
+      <c r="AH27" s="116"/>
+      <c r="AI27" s="117"/>
+      <c r="AJ27" s="117"/>
+      <c r="AK27" s="118"/>
+      <c r="AL27" s="116"/>
+      <c r="AM27" s="117"/>
+      <c r="AN27" s="117"/>
+      <c r="AO27" s="118"/>
       <c r="AP27" s="31"/>
       <c r="AQ27" s="27"/>
       <c r="AR27" s="27"/>
@@ -6989,17 +7061,17 @@
       <c r="AB28" s="39"/>
       <c r="AC28" s="39"/>
       <c r="AD28" s="41"/>
-      <c r="AE28" s="2"/>
-      <c r="AF28" s="3"/>
-      <c r="AG28" s="3"/>
-      <c r="AH28" s="2"/>
-      <c r="AI28" s="3"/>
-      <c r="AJ28" s="3"/>
-      <c r="AK28" s="4"/>
-      <c r="AL28" s="2"/>
-      <c r="AM28" s="3"/>
-      <c r="AN28" s="3"/>
-      <c r="AO28" s="4"/>
+      <c r="AE28" s="113"/>
+      <c r="AF28" s="114"/>
+      <c r="AG28" s="115"/>
+      <c r="AH28" s="113"/>
+      <c r="AI28" s="114"/>
+      <c r="AJ28" s="114"/>
+      <c r="AK28" s="115"/>
+      <c r="AL28" s="113"/>
+      <c r="AM28" s="114"/>
+      <c r="AN28" s="114"/>
+      <c r="AO28" s="115"/>
       <c r="AP28" s="38"/>
       <c r="AQ28" s="39"/>
       <c r="AR28" s="39"/>
@@ -7186,17 +7258,23 @@
       <c r="AB29" s="27"/>
       <c r="AC29" s="27"/>
       <c r="AD29" s="32"/>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="12"/>
-      <c r="AG29" s="12"/>
-      <c r="AH29" s="11"/>
-      <c r="AI29" s="12"/>
-      <c r="AJ29" s="12"/>
-      <c r="AK29" s="13"/>
-      <c r="AL29" s="11"/>
-      <c r="AM29" s="12"/>
-      <c r="AN29" s="12"/>
-      <c r="AO29" s="13"/>
+      <c r="AE29" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF29" s="110"/>
+      <c r="AG29" s="111"/>
+      <c r="AH29" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI29" s="110"/>
+      <c r="AJ29" s="110"/>
+      <c r="AK29" s="111"/>
+      <c r="AL29" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM29" s="110"/>
+      <c r="AN29" s="110"/>
+      <c r="AO29" s="111"/>
       <c r="AP29" s="31"/>
       <c r="AQ29" s="27"/>
       <c r="AR29" s="27"/>
@@ -7379,17 +7457,17 @@
       <c r="AB30" s="39"/>
       <c r="AC30" s="39"/>
       <c r="AD30" s="41"/>
-      <c r="AE30" s="14"/>
-      <c r="AF30" s="15"/>
-      <c r="AG30" s="15"/>
-      <c r="AH30" s="14"/>
-      <c r="AI30" s="15"/>
-      <c r="AJ30" s="15"/>
-      <c r="AK30" s="16"/>
-      <c r="AL30" s="14"/>
-      <c r="AM30" s="15"/>
-      <c r="AN30" s="15"/>
-      <c r="AO30" s="16"/>
+      <c r="AE30" s="113"/>
+      <c r="AF30" s="114"/>
+      <c r="AG30" s="115"/>
+      <c r="AH30" s="113"/>
+      <c r="AI30" s="114"/>
+      <c r="AJ30" s="114"/>
+      <c r="AK30" s="115"/>
+      <c r="AL30" s="113"/>
+      <c r="AM30" s="114"/>
+      <c r="AN30" s="114"/>
+      <c r="AO30" s="115"/>
       <c r="AP30" s="38"/>
       <c r="AQ30" s="39"/>
       <c r="AR30" s="39"/>
@@ -7780,15 +7858,15 @@
       <c r="AC32" s="48"/>
       <c r="AD32" s="51"/>
       <c r="AE32" s="2"/>
-      <c r="AF32" s="20"/>
-      <c r="AG32" s="20"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
       <c r="AH32" s="2"/>
-      <c r="AI32" s="20"/>
-      <c r="AJ32" s="20"/>
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="3"/>
       <c r="AK32" s="4"/>
       <c r="AL32" s="2"/>
-      <c r="AM32" s="20"/>
-      <c r="AN32" s="20"/>
+      <c r="AM32" s="3"/>
+      <c r="AN32" s="3"/>
       <c r="AO32" s="4"/>
       <c r="AP32" s="31"/>
       <c r="AQ32" s="27"/>
@@ -8172,15 +8250,15 @@
       <c r="AC34" s="27"/>
       <c r="AD34" s="32"/>
       <c r="AE34" s="2"/>
-      <c r="AF34" s="20"/>
-      <c r="AG34" s="20"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
       <c r="AH34" s="2"/>
-      <c r="AI34" s="20"/>
-      <c r="AJ34" s="20"/>
+      <c r="AI34" s="3"/>
+      <c r="AJ34" s="3"/>
       <c r="AK34" s="4"/>
       <c r="AL34" s="2"/>
-      <c r="AM34" s="20"/>
-      <c r="AN34" s="20"/>
+      <c r="AM34" s="3"/>
+      <c r="AN34" s="3"/>
       <c r="AO34" s="4"/>
       <c r="AP34" s="31"/>
       <c r="AQ34" s="27"/>
@@ -8367,15 +8445,15 @@
       <c r="AC35" s="27"/>
       <c r="AD35" s="32"/>
       <c r="AE35" s="2"/>
-      <c r="AF35" s="20"/>
-      <c r="AG35" s="20"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3"/>
       <c r="AH35" s="2"/>
-      <c r="AI35" s="20"/>
-      <c r="AJ35" s="20"/>
+      <c r="AI35" s="3"/>
+      <c r="AJ35" s="3"/>
       <c r="AK35" s="4"/>
       <c r="AL35" s="2"/>
-      <c r="AM35" s="20"/>
-      <c r="AN35" s="20"/>
+      <c r="AM35" s="3"/>
+      <c r="AN35" s="3"/>
       <c r="AO35" s="4"/>
       <c r="AP35" s="31"/>
       <c r="AQ35" s="27"/>
@@ -9984,15 +10062,15 @@
       <c r="AC44" s="27"/>
       <c r="AD44" s="32"/>
       <c r="AE44" s="2"/>
-      <c r="AF44" s="20"/>
-      <c r="AG44" s="20"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="3"/>
       <c r="AH44" s="2"/>
-      <c r="AI44" s="20"/>
-      <c r="AJ44" s="20"/>
+      <c r="AI44" s="3"/>
+      <c r="AJ44" s="3"/>
       <c r="AK44" s="4"/>
       <c r="AL44" s="2"/>
-      <c r="AM44" s="20"/>
-      <c r="AN44" s="20"/>
+      <c r="AM44" s="3"/>
+      <c r="AN44" s="3"/>
       <c r="AO44" s="4"/>
       <c r="AP44" s="31"/>
       <c r="AQ44" s="27"/>
@@ -10880,15 +10958,15 @@
       <c r="AC49" s="48"/>
       <c r="AD49" s="51"/>
       <c r="AE49" s="2"/>
-      <c r="AF49" s="20"/>
-      <c r="AG49" s="20"/>
+      <c r="AF49" s="3"/>
+      <c r="AG49" s="3"/>
       <c r="AH49" s="2"/>
-      <c r="AI49" s="20"/>
-      <c r="AJ49" s="20"/>
+      <c r="AI49" s="3"/>
+      <c r="AJ49" s="3"/>
       <c r="AK49" s="4"/>
       <c r="AL49" s="2"/>
-      <c r="AM49" s="20"/>
-      <c r="AN49" s="20"/>
+      <c r="AM49" s="3"/>
+      <c r="AN49" s="3"/>
       <c r="AO49" s="4"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="27"/>
@@ -11369,17 +11447,23 @@
       <c r="AB52" s="44"/>
       <c r="AC52" s="44"/>
       <c r="AD52" s="47"/>
-      <c r="AE52" s="2"/>
-      <c r="AF52" s="3"/>
-      <c r="AG52" s="3"/>
-      <c r="AH52" s="2"/>
-      <c r="AI52" s="3"/>
-      <c r="AJ52" s="3"/>
-      <c r="AK52" s="4"/>
-      <c r="AL52" s="2"/>
-      <c r="AM52" s="3"/>
-      <c r="AN52" s="3"/>
-      <c r="AO52" s="4"/>
+      <c r="AE52" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF52" s="110"/>
+      <c r="AG52" s="111"/>
+      <c r="AH52" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI52" s="110"/>
+      <c r="AJ52" s="110"/>
+      <c r="AK52" s="111"/>
+      <c r="AL52" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM52" s="110"/>
+      <c r="AN52" s="110"/>
+      <c r="AO52" s="111"/>
       <c r="AP52" s="31"/>
       <c r="AQ52" s="27"/>
       <c r="AR52" s="27"/>
@@ -11533,17 +11617,17 @@
       <c r="AB53" s="44"/>
       <c r="AC53" s="44"/>
       <c r="AD53" s="47"/>
-      <c r="AE53" s="2"/>
-      <c r="AF53" s="20"/>
-      <c r="AG53" s="20"/>
-      <c r="AH53" s="2"/>
-      <c r="AI53" s="20"/>
-      <c r="AJ53" s="20"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="2"/>
-      <c r="AM53" s="20"/>
-      <c r="AN53" s="20"/>
-      <c r="AO53" s="4"/>
+      <c r="AE53" s="116"/>
+      <c r="AF53" s="117"/>
+      <c r="AG53" s="118"/>
+      <c r="AH53" s="116"/>
+      <c r="AI53" s="117"/>
+      <c r="AJ53" s="117"/>
+      <c r="AK53" s="118"/>
+      <c r="AL53" s="116"/>
+      <c r="AM53" s="117"/>
+      <c r="AN53" s="117"/>
+      <c r="AO53" s="118"/>
       <c r="AP53" s="31"/>
       <c r="AQ53" s="27"/>
       <c r="AR53" s="27"/>
@@ -11695,17 +11779,17 @@
       <c r="AB54" s="44"/>
       <c r="AC54" s="44"/>
       <c r="AD54" s="47"/>
-      <c r="AE54" s="2"/>
-      <c r="AF54" s="3"/>
-      <c r="AG54" s="3"/>
-      <c r="AH54" s="2"/>
-      <c r="AI54" s="3"/>
-      <c r="AJ54" s="3"/>
-      <c r="AK54" s="4"/>
-      <c r="AL54" s="2"/>
-      <c r="AM54" s="3"/>
-      <c r="AN54" s="3"/>
-      <c r="AO54" s="4"/>
+      <c r="AE54" s="116"/>
+      <c r="AF54" s="117"/>
+      <c r="AG54" s="118"/>
+      <c r="AH54" s="116"/>
+      <c r="AI54" s="117"/>
+      <c r="AJ54" s="117"/>
+      <c r="AK54" s="118"/>
+      <c r="AL54" s="116"/>
+      <c r="AM54" s="117"/>
+      <c r="AN54" s="117"/>
+      <c r="AO54" s="118"/>
       <c r="AP54" s="31"/>
       <c r="AQ54" s="27"/>
       <c r="AR54" s="27"/>
@@ -11882,17 +11966,17 @@
       <c r="AB55" s="44"/>
       <c r="AC55" s="44"/>
       <c r="AD55" s="47"/>
-      <c r="AE55" s="2"/>
-      <c r="AF55" s="3"/>
-      <c r="AG55" s="3"/>
-      <c r="AH55" s="2"/>
-      <c r="AI55" s="3"/>
-      <c r="AJ55" s="3"/>
-      <c r="AK55" s="4"/>
-      <c r="AL55" s="2"/>
-      <c r="AM55" s="3"/>
-      <c r="AN55" s="3"/>
-      <c r="AO55" s="4"/>
+      <c r="AE55" s="116"/>
+      <c r="AF55" s="117"/>
+      <c r="AG55" s="118"/>
+      <c r="AH55" s="116"/>
+      <c r="AI55" s="117"/>
+      <c r="AJ55" s="117"/>
+      <c r="AK55" s="118"/>
+      <c r="AL55" s="116"/>
+      <c r="AM55" s="117"/>
+      <c r="AN55" s="117"/>
+      <c r="AO55" s="118"/>
       <c r="AP55" s="31"/>
       <c r="AQ55" s="27"/>
       <c r="AR55" s="27"/>
@@ -12069,17 +12153,17 @@
       <c r="AB56" s="44"/>
       <c r="AC56" s="44"/>
       <c r="AD56" s="47"/>
-      <c r="AE56" s="2"/>
-      <c r="AF56" s="3"/>
-      <c r="AG56" s="3"/>
-      <c r="AH56" s="2"/>
-      <c r="AI56" s="3"/>
-      <c r="AJ56" s="3"/>
-      <c r="AK56" s="4"/>
-      <c r="AL56" s="2"/>
-      <c r="AM56" s="3"/>
-      <c r="AN56" s="3"/>
-      <c r="AO56" s="4"/>
+      <c r="AE56" s="116"/>
+      <c r="AF56" s="117"/>
+      <c r="AG56" s="118"/>
+      <c r="AH56" s="116"/>
+      <c r="AI56" s="117"/>
+      <c r="AJ56" s="117"/>
+      <c r="AK56" s="118"/>
+      <c r="AL56" s="116"/>
+      <c r="AM56" s="117"/>
+      <c r="AN56" s="117"/>
+      <c r="AO56" s="118"/>
       <c r="AP56" s="31"/>
       <c r="AQ56" s="27"/>
       <c r="AR56" s="27"/>
@@ -12256,17 +12340,17 @@
       <c r="AB57" s="43"/>
       <c r="AC57" s="43"/>
       <c r="AD57" s="61"/>
-      <c r="AE57" s="14"/>
-      <c r="AF57" s="15"/>
-      <c r="AG57" s="15"/>
-      <c r="AH57" s="14"/>
-      <c r="AI57" s="15"/>
-      <c r="AJ57" s="15"/>
-      <c r="AK57" s="16"/>
-      <c r="AL57" s="14"/>
-      <c r="AM57" s="15"/>
-      <c r="AN57" s="15"/>
-      <c r="AO57" s="16"/>
+      <c r="AE57" s="113"/>
+      <c r="AF57" s="114"/>
+      <c r="AG57" s="115"/>
+      <c r="AH57" s="113"/>
+      <c r="AI57" s="114"/>
+      <c r="AJ57" s="114"/>
+      <c r="AK57" s="115"/>
+      <c r="AL57" s="113"/>
+      <c r="AM57" s="114"/>
+      <c r="AN57" s="114"/>
+      <c r="AO57" s="115"/>
       <c r="AP57" s="38"/>
       <c r="AQ57" s="39"/>
       <c r="AR57" s="39"/>
@@ -12449,17 +12533,23 @@
       <c r="AB58" s="44"/>
       <c r="AC58" s="44"/>
       <c r="AD58" s="47"/>
-      <c r="AE58" s="2"/>
-      <c r="AF58" s="3"/>
-      <c r="AG58" s="3"/>
-      <c r="AH58" s="2"/>
-      <c r="AI58" s="3"/>
-      <c r="AJ58" s="3"/>
-      <c r="AK58" s="4"/>
-      <c r="AL58" s="2"/>
-      <c r="AM58" s="3"/>
-      <c r="AN58" s="3"/>
-      <c r="AO58" s="4"/>
+      <c r="AE58" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF58" s="110"/>
+      <c r="AG58" s="111"/>
+      <c r="AH58" s="112">
+        <v>45590</v>
+      </c>
+      <c r="AI58" s="110"/>
+      <c r="AJ58" s="110"/>
+      <c r="AK58" s="111"/>
+      <c r="AL58" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM58" s="110"/>
+      <c r="AN58" s="110"/>
+      <c r="AO58" s="111"/>
       <c r="AP58" s="31"/>
       <c r="AQ58" s="27"/>
       <c r="AR58" s="27"/>
@@ -12636,17 +12726,17 @@
       <c r="AB59" s="44"/>
       <c r="AC59" s="44"/>
       <c r="AD59" s="47"/>
-      <c r="AE59" s="2"/>
-      <c r="AF59" s="3"/>
-      <c r="AG59" s="3"/>
-      <c r="AH59" s="2"/>
-      <c r="AI59" s="3"/>
-      <c r="AJ59" s="3"/>
-      <c r="AK59" s="4"/>
-      <c r="AL59" s="2"/>
-      <c r="AM59" s="3"/>
-      <c r="AN59" s="3"/>
-      <c r="AO59" s="4"/>
+      <c r="AE59" s="116"/>
+      <c r="AF59" s="117"/>
+      <c r="AG59" s="118"/>
+      <c r="AH59" s="116"/>
+      <c r="AI59" s="117"/>
+      <c r="AJ59" s="117"/>
+      <c r="AK59" s="118"/>
+      <c r="AL59" s="116"/>
+      <c r="AM59" s="117"/>
+      <c r="AN59" s="117"/>
+      <c r="AO59" s="118"/>
       <c r="AP59" s="31"/>
       <c r="AQ59" s="27"/>
       <c r="AR59" s="27"/>
@@ -12823,17 +12913,17 @@
       <c r="AB60" s="43"/>
       <c r="AC60" s="43"/>
       <c r="AD60" s="61"/>
-      <c r="AE60" s="14"/>
-      <c r="AF60" s="15"/>
-      <c r="AG60" s="15"/>
-      <c r="AH60" s="14"/>
-      <c r="AI60" s="15"/>
-      <c r="AJ60" s="15"/>
-      <c r="AK60" s="16"/>
-      <c r="AL60" s="14"/>
-      <c r="AM60" s="15"/>
-      <c r="AN60" s="15"/>
-      <c r="AO60" s="16"/>
+      <c r="AE60" s="113"/>
+      <c r="AF60" s="114"/>
+      <c r="AG60" s="115"/>
+      <c r="AH60" s="113"/>
+      <c r="AI60" s="114"/>
+      <c r="AJ60" s="114"/>
+      <c r="AK60" s="115"/>
+      <c r="AL60" s="113"/>
+      <c r="AM60" s="114"/>
+      <c r="AN60" s="114"/>
+      <c r="AO60" s="115"/>
       <c r="AP60" s="38"/>
       <c r="AQ60" s="39"/>
       <c r="AR60" s="39"/>
@@ -13746,15 +13836,15 @@
       <c r="AC65" s="48"/>
       <c r="AD65" s="51"/>
       <c r="AE65" s="2"/>
-      <c r="AF65" s="20"/>
-      <c r="AG65" s="20"/>
+      <c r="AF65" s="3"/>
+      <c r="AG65" s="3"/>
       <c r="AH65" s="2"/>
-      <c r="AI65" s="20"/>
-      <c r="AJ65" s="20"/>
+      <c r="AI65" s="3"/>
+      <c r="AJ65" s="3"/>
       <c r="AK65" s="4"/>
       <c r="AL65" s="2"/>
-      <c r="AM65" s="20"/>
-      <c r="AN65" s="20"/>
+      <c r="AM65" s="3"/>
+      <c r="AN65" s="3"/>
       <c r="AO65" s="4"/>
       <c r="AP65" s="31"/>
       <c r="AQ65" s="27"/>
@@ -14402,15 +14492,15 @@
       <c r="AC69" s="48"/>
       <c r="AD69" s="51"/>
       <c r="AE69" s="2"/>
-      <c r="AF69" s="20"/>
-      <c r="AG69" s="20"/>
+      <c r="AF69" s="3"/>
+      <c r="AG69" s="3"/>
       <c r="AH69" s="2"/>
-      <c r="AI69" s="20"/>
-      <c r="AJ69" s="20"/>
+      <c r="AI69" s="3"/>
+      <c r="AJ69" s="3"/>
       <c r="AK69" s="4"/>
       <c r="AL69" s="2"/>
-      <c r="AM69" s="20"/>
-      <c r="AN69" s="20"/>
+      <c r="AM69" s="3"/>
+      <c r="AN69" s="3"/>
       <c r="AO69" s="4"/>
       <c r="AP69" s="31"/>
       <c r="AQ69" s="27"/>
@@ -15829,22 +15919,50 @@
       <c r="GA76" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="I10:S10"/>
-    <mergeCell ref="T10:AD10"/>
-    <mergeCell ref="FN10:FQ10"/>
-    <mergeCell ref="AE10:AG10"/>
-    <mergeCell ref="AH10:AK10"/>
-    <mergeCell ref="AL10:AO10"/>
-    <mergeCell ref="BW10:BY10"/>
-    <mergeCell ref="BZ10:CC10"/>
-    <mergeCell ref="CD10:CG10"/>
-    <mergeCell ref="DO10:DQ10"/>
-    <mergeCell ref="DR10:DU10"/>
-    <mergeCell ref="EV10:FF10"/>
-    <mergeCell ref="BA10:BK10"/>
-    <mergeCell ref="BL10:BV10"/>
+  <mergeCells count="74">
+    <mergeCell ref="AE58:AG60"/>
+    <mergeCell ref="AH58:AK60"/>
+    <mergeCell ref="AL58:AO60"/>
+    <mergeCell ref="AE29:AG30"/>
+    <mergeCell ref="AH29:AK30"/>
+    <mergeCell ref="AL29:AO30"/>
+    <mergeCell ref="AE52:AG57"/>
+    <mergeCell ref="AH52:AK57"/>
+    <mergeCell ref="AL52:AO57"/>
+    <mergeCell ref="AE21:AG23"/>
+    <mergeCell ref="AH21:AK23"/>
+    <mergeCell ref="AL21:AO23"/>
+    <mergeCell ref="AE24:AG28"/>
+    <mergeCell ref="AH24:AK28"/>
+    <mergeCell ref="AL24:AO28"/>
+    <mergeCell ref="AE15:AG17"/>
+    <mergeCell ref="AH15:AK17"/>
+    <mergeCell ref="AL15:AO17"/>
+    <mergeCell ref="AE18:AG20"/>
+    <mergeCell ref="AH18:AK20"/>
+    <mergeCell ref="AL18:AO20"/>
+    <mergeCell ref="AE11:AG12"/>
+    <mergeCell ref="AH11:AK12"/>
+    <mergeCell ref="AL11:AO12"/>
+    <mergeCell ref="AE13:AG14"/>
+    <mergeCell ref="AH13:AK14"/>
+    <mergeCell ref="AL13:AO14"/>
+    <mergeCell ref="BE1:BH2"/>
+    <mergeCell ref="AP10:AY10"/>
+    <mergeCell ref="X1:AM1"/>
+    <mergeCell ref="X2:AM2"/>
+    <mergeCell ref="H8:AY8"/>
+    <mergeCell ref="H9:AY9"/>
+    <mergeCell ref="A1:S2"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="AN1:AQ1"/>
+    <mergeCell ref="AR1:BA1"/>
+    <mergeCell ref="BB1:BD2"/>
+    <mergeCell ref="AN2:AQ2"/>
+    <mergeCell ref="AR2:BA2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:W4"/>
     <mergeCell ref="FR10:GA10"/>
     <mergeCell ref="EJ8:GA8"/>
     <mergeCell ref="EJ9:GA9"/>
@@ -15861,22 +15979,21 @@
     <mergeCell ref="DV10:DY10"/>
     <mergeCell ref="FG10:FI10"/>
     <mergeCell ref="FJ10:FM10"/>
-    <mergeCell ref="BE1:BH2"/>
-    <mergeCell ref="AP10:AY10"/>
-    <mergeCell ref="X1:AM1"/>
-    <mergeCell ref="X2:AM2"/>
-    <mergeCell ref="H8:AY8"/>
-    <mergeCell ref="H9:AY9"/>
-    <mergeCell ref="A1:S2"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="AN1:AQ1"/>
-    <mergeCell ref="AR1:BA1"/>
-    <mergeCell ref="BB1:BD2"/>
-    <mergeCell ref="AN2:AQ2"/>
-    <mergeCell ref="AR2:BA2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:W4"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="I10:S10"/>
+    <mergeCell ref="T10:AD10"/>
+    <mergeCell ref="FN10:FQ10"/>
+    <mergeCell ref="AE10:AG10"/>
+    <mergeCell ref="AH10:AK10"/>
+    <mergeCell ref="AL10:AO10"/>
+    <mergeCell ref="BW10:BY10"/>
+    <mergeCell ref="BZ10:CC10"/>
+    <mergeCell ref="CD10:CG10"/>
+    <mergeCell ref="DO10:DQ10"/>
+    <mergeCell ref="DR10:DU10"/>
+    <mergeCell ref="EV10:FF10"/>
+    <mergeCell ref="BA10:BK10"/>
+    <mergeCell ref="BL10:BV10"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
